--- a/output/reports/e2e/E2E_Results.xlsx
+++ b/output/reports/e2e/E2E_Results.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.129</v>
+        <v>0.18</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.525</v>
+        <v>0.479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Method 1 512bp (2.9%) | Method 2 386bp (2.2%) -&gt; 2.9% (METHOD_1)</t>
+          <t>proposal: M1 388bp (2.0%) | M2 664bp (3.4%) -&gt; 3.4% (METHOD_2); current rule M2 779bp -&gt; 4.0%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -708,7 +708,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ratios, buffers, PCA</t>
+          <t>CCAR stress test</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CET1 12.22%  T1 13.63%  Total 16.37%  SLR 5.91%  PCA WELL_CAPITALIZED</t>
+          <t>severely adverse min CET1 6.71% (Q9), SCB 5.51%, pass=True</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -729,7 +729,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Large exposures (SCCL)</t>
+          <t>Ratios, buffers, PCA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -738,11 +738,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30 counterparties, 23 reportable, 1 limit breaches, largest 18.4% of T1</t>
+          <t>CET1 12.22%  T1 13.63%  Total 16.37%  SLR 5.91%  PCA WELL_CAPITALIZED</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -750,7 +750,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CCAR stress test</t>
+          <t>Large exposures (SCCL)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,11 +759,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>severely adverse min CET1 6.71% (Q9), SCB 5.51%, pass=True</t>
+          <t>30 counterparties, 23 reportable, 1 limit breaches, largest 18.4% of T1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>reports: FR_Y_9C, FFIEC_101, FR_Y_15, FR_Y_14 | cross-validation 3/4 | DQ pass=False</t>
+          <t>reports: FR_Y_9C, FFIEC_101, FR_Y_15, FR_Y_14 | cross-validation 4/4 | DQ pass=True</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5 templates: OV1, KM1, MR1, LR1, LR2 | not produced: MR2, MR3, MR4</t>
+          <t>5 templates: OV1, KM1, MR1, LR1, LR2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'base_report': {'reporting_date': datetime.date(2026, 6, 30), 'total_rwa': 1701563.681729855, 'credit_risk_rwa': 1191868.0111048662, 'market_risk_rwa': 205948.60179119706, 'operational_risk_rwa': 177330.0, 'cva_risk_rwa': 126417.0688337919, 'cet1_ratio': 0.1222405027994848, 'tier1_ratio': 0.13634517619942535, 'total_capital_ratio': 0.16374612305144212, 'leverage_ratio': 0.05912372751928002}, 'ccb_requirement': 0.032, 'ccyb_requirement': 0.0, 'gsib_surcharge': 0.029000000000000005, 'combined_buffer': 0.061000000000000006, 'effective_cet1_minimum': 0.10600000000000001, 'effective_tier1_minimum': 0.121, 'effective_total_minimum': 0.14100000000000001, 'cet1_surplus_over_minimum': 131429.63432215655, 'cet1_surplus_over_buffer': 27634.249736635364, 'pca_category': 'WELL_CAPITALIZED', 'is_well_capitalized': True}</t>
+          <t>{'base_report': {'reporting_date': datetime.date(2026, 6, 30), 'total_rwa': 1701563.681729855, 'credit_risk_rwa': 1191868.0111048662, 'market_risk_rwa': 205948.60179119706, 'operational_risk_rwa': 177330.0, 'cva_risk_rwa': 126417.0688337919, 'cet1_ratio': 0.1222405027994848, 'tier1_ratio': 0.13634517619942535, 'total_capital_ratio': 0.16374612305144212, 'leverage_ratio': 0.05912372751928002}, 'ccb_requirement': 0.05514489282987152, 'ccyb_requirement': 0.0, 'gsib_surcharge': 0.034, 'combined_buffer': 0.08914489282987152, 'effective_cet1_minimum': 0.13414489282987152, 'effective_tier1_minimum': 0.14914489282987153, 'effective_total_minimum': 0.16914489282987152, 'cet1_surplus_over_minimum': 131429.63432215655, 'cet1_surplus_over_buffer': -20256.077728853008, 'pca_category': 'WELL_CAPITALIZED', 'is_well_capitalized': True}</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,19 +1692,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.029 in [0.010, 0.050]</t>
+          <t>0.034 in [0.010, 0.050]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ratios, buffers, PCA</t>
+          <t>G-SIB surcharge</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CET1 ratio (CLAUDE.md 10-15%)</t>
+          <t>identified as GSIB (method 1 &gt;= 130 bp)</t>
         </is>
       </c>
       <c r="C26" t="b">
@@ -1712,19 +1712,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.1222 in [0.1000, 0.1500]</t>
+          <t>388 in [130, 2000]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ratios, buffers, PCA</t>
+          <t>G-SIB surcharge</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SLR (CLAUDE.md 5-7%)</t>
+          <t>proposal lowers method 2 score vs current rule</t>
         </is>
       </c>
       <c r="C27" t="b">
@@ -1732,19 +1732,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.0591 in [0.0500, 0.0700]</t>
+          <t>0.853 in [0.000, 1.000]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Large exposures (SCCL)</t>
+          <t>CCAR stress test</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>counterparties assessed</t>
+          <t>severely adverse min CET1 &gt;= 4.5%</t>
         </is>
       </c>
       <c r="C28" t="b">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>40 in [40, 40]</t>
+          <t>0.0671 in [0.0450, 0.2000]</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>severely adverse min CET1 &gt;= 4.5%</t>
+          <t>SCB floor 2.5%</t>
         </is>
       </c>
       <c r="C29" t="b">
@@ -1772,19 +1772,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.0671 in [0.0450, 0.2000]</t>
+          <t>0.0551 in [0.0250, 0.1000]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CCAR stress test</t>
+          <t>Ratios, buffers, PCA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SCB floor 2.5%</t>
+          <t>CET1 ratio (CLAUDE.md 10-15%)</t>
         </is>
       </c>
       <c r="C30" t="b">
@@ -1792,19 +1792,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.0551 in [0.0250, 0.1000]</t>
+          <t>0.1222 in [0.1000, 0.1500]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fed reports (Y-9C, 101, Y-15, Y-14)</t>
+          <t>Ratios, buffers, PCA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>four Fed reports generated</t>
+          <t>SLR (CLAUDE.md 5-7%)</t>
         </is>
       </c>
       <c r="C31" t="b">
@@ -1812,25 +1812,85 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4 in [4, 10]</t>
+          <t>0.0591 in [0.0500, 0.0700]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Ratios, buffers, PCA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SCB in buffer stack = stress-test SCB</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.0551 in [0.0551, 0.0551]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Large exposures (SCCL)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>counterparties assessed</t>
+        </is>
+      </c>
+      <c r="C33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>40 in [40, 40]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Fed reports (Y-9C, 101, Y-15, Y-14)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>four Fed reports generated</t>
+        </is>
+      </c>
+      <c r="C34" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4 in [4, 10]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Pillar 3 disclosures</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Pillar 3 templates produced</t>
         </is>
       </c>
-      <c r="C32" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>5 in [4, 40]</t>
         </is>
@@ -2075,7 +2135,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.032</v>
+        <v>0.05514489282987152</v>
       </c>
     </row>
     <row r="7">
@@ -2095,7 +2155,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="9">
@@ -2105,7 +2165,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.032</v>
+        <v>0.05514489282987152</v>
       </c>
     </row>
     <row r="10">
@@ -2115,7 +2175,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06100000000000001</v>
+        <v>0.08914489282987152</v>
       </c>
     </row>
     <row r="11">
@@ -2125,7 +2185,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.106</v>
+        <v>0.1341448928298715</v>
       </c>
     </row>
     <row r="12">
@@ -2135,7 +2195,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.121</v>
+        <v>0.1491448928298715</v>
       </c>
     </row>
     <row r="13">
@@ -2145,7 +2205,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.141</v>
+        <v>0.1691448928298715</v>
       </c>
     </row>
   </sheetData>
@@ -17299,7 +17359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17437,67 +17497,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>drc_total</t>
+          <t>drc_sec_nonctp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>135.6991729661765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rrao_total</t>
+          <t>drc_sec_ctp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>girr_delta</t>
+          <t>drc_total</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4436.48015403459</v>
+        <v>135.6991729661765</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>girr_vega</t>
+          <t>rrao_total</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>girr_curvature</t>
+          <t>girr_delta</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>4436.48015403459</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>csr_nonsec_delta</t>
+          <t>girr_vega</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9712.155222229752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>csr_nonsec_vega</t>
+          <t>girr_curvature</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -17507,17 +17567,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>csr_nonsec_curvature</t>
+          <t>csr_nonsec_delta</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>9712.155222229752</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>csr_sec_nonctp_delta</t>
+          <t>csr_nonsec_vega</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -17527,7 +17587,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>csr_sec_nonctp_vega</t>
+          <t>csr_nonsec_curvature</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -17537,7 +17597,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>csr_sec_nonctp_curvature</t>
+          <t>csr_sec_nonctp_delta</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -17547,7 +17607,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>csr_sec_ctp_delta</t>
+          <t>csr_sec_nonctp_vega</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -17557,7 +17617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>csr_sec_ctp_vega</t>
+          <t>csr_sec_nonctp_curvature</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -17567,7 +17627,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>csr_sec_ctp_curvature</t>
+          <t>csr_sec_ctp_delta</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -17577,90 +17637,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>equity_delta</t>
+          <t>csr_sec_ctp_vega</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>882.3409430639695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>equity_vega</t>
+          <t>csr_sec_ctp_curvature</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20.32782151102937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>equity_curvature</t>
+          <t>equity_delta</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.14713475736083</v>
+        <v>882.3409430639695</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>commodity_delta</t>
+          <t>equity_vega</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>930.7263431866077</v>
+        <v>20.32782151102937</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>commodity_vega</t>
+          <t>equity_curvature</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>3.14713475736083</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>commodity_curvature</t>
+          <t>commodity_delta</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>930.7263431866077</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fx_delta</t>
+          <t>commodity_vega</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>238.137345255775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fx_vega</t>
+          <t>commodity_curvature</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>36.87400629050508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>fx_delta</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>238.137345255775</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fx_vega</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36.87400629050508</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>fx_curvature</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B38" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/reports/e2e/E2E_Results.xlsx
+++ b/output/reports/e2e/E2E_Results.xlsx
@@ -17,7 +17,11 @@
     <sheet name="FRTB" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="OpRisk" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="FFIEC101_SchedA" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="FR_Y9C" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Jurisdictions_2027" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Jurisdictions_2030" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Jurisdiction_Credit" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Output_Floor_WhatIf" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="FR_Y9C" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +469,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -507,7 +511,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -528,7 +532,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.18</v>
+        <v>0.122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -549,7 +553,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -612,7 +616,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.479</v>
+        <v>0.598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -633,7 +637,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -809,6 +813,27 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BCBS CET1 11.5% | US CET1 13.1% | UK CET1 12.7% | EU CET1 12.2% | SG CET1 11.6% | CA CET1 11.7%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1057,6 +1082,3915 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AA7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>regime_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fx_usd_to_local</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>credit_exposure</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>credit_rwa</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ccr_ead</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ccr_rwa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>cva_rwa</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>op_business_indicator</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>op_ilm</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>op_rwa</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>market_rwa</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>securitisation_rwa</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>standardised_rwa</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>modelled_rwa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>floor_applies</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>floor_factor</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>floor_add_on</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>total_rwa</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>cet1_ratio</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tier1_ratio</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>total_capital_ratio</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>leverage_ratio</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>cet1_requirement</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>cet1_surplus</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>leverage_requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Basel Framework (BCBS consolidated standards)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9625565501973241</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2048274.807488002</v>
+      </c>
+      <c r="F2" t="n">
+        <v>901803.3739777341</v>
+      </c>
+      <c r="G2" t="n">
+        <v>276492.0462706767</v>
+      </c>
+      <c r="H2" t="n">
+        <v>172165.0586869715</v>
+      </c>
+      <c r="I2" t="n">
+        <v>127321.2539232395</v>
+      </c>
+      <c r="J2" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.295601582145034</v>
+      </c>
+      <c r="L2" t="n">
+        <v>332124.599064379</v>
+      </c>
+      <c r="M2" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N2" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.1152901737067579</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1285928860575376</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.154435874673844</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.02529017370675789</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>US ERBA NPR (March 2026)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2048274.807488005</v>
+      </c>
+      <c r="F3" t="n">
+        <v>871268.6051329094</v>
+      </c>
+      <c r="G3" t="n">
+        <v>230658.8481670908</v>
+      </c>
+      <c r="H3" t="n">
+        <v>127420.2356700461</v>
+      </c>
+      <c r="I3" t="n">
+        <v>127321.2539232394</v>
+      </c>
+      <c r="J3" t="n">
+        <v>89766.66666666667</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>190350</v>
+      </c>
+      <c r="M3" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N3" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1310575395549625</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1461795633497659</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1755569022322165</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1341448928298715</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.003087353274908972</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UK PRA Basel 3.1 (PS1/26)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7981326402926173</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2048274.807488003</v>
+      </c>
+      <c r="F4" t="n">
+        <v>873950.8353108931</v>
+      </c>
+      <c r="G4" t="n">
+        <v>230658.8481670908</v>
+      </c>
+      <c r="H4" t="n">
+        <v>137790.160109282</v>
+      </c>
+      <c r="I4" t="n">
+        <v>105594.1599143253</v>
+      </c>
+      <c r="J4" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>255795.5202730408</v>
+      </c>
+      <c r="M4" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N4" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1643859.738104304</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1643859.738104304</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1265314766087435</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1411312623712908</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1694940569137066</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.03653147660874351</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EU CRR3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9625565501973241</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2040893.05163271</v>
+      </c>
+      <c r="F5" t="n">
+        <v>884032.0202693905</v>
+      </c>
+      <c r="G5" t="n">
+        <v>276492.0462706767</v>
+      </c>
+      <c r="H5" t="n">
+        <v>172165.0586869715</v>
+      </c>
+      <c r="I5" t="n">
+        <v>127321.2539232395</v>
+      </c>
+      <c r="J5" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>256347.7874999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N5" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1710595.182876365</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1710595.182876365</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1215951044888646</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1356253088529644</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1628815857764167</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.0315951044888646</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 (Singapore Basel III final reforms)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.36336509769949</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2048274.807488003</v>
+      </c>
+      <c r="F6" t="n">
+        <v>895989.3374913485</v>
+      </c>
+      <c r="G6" t="n">
+        <v>276492.0462706767</v>
+      </c>
+      <c r="H6" t="n">
+        <v>172165.0586869716</v>
+      </c>
+      <c r="I6" t="n">
+        <v>127321.2539232394</v>
+      </c>
+      <c r="J6" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.296782087274663</v>
+      </c>
+      <c r="L6" t="n">
+        <v>331502.8314298259</v>
+      </c>
+      <c r="M6" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N6" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1797707.544028149</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1797707.544028149</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1157029132413449</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.129053249384577</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1549887560598895</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.005702913241344851</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OSFI Capital Adequacy Requirements (CAR) 2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.43882953123496</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2048274.807488004</v>
+      </c>
+      <c r="F7" t="n">
+        <v>876268.2860719626</v>
+      </c>
+      <c r="G7" t="n">
+        <v>276492.0462706767</v>
+      </c>
+      <c r="H7" t="n">
+        <v>172165.0586869716</v>
+      </c>
+      <c r="I7" t="n">
+        <v>127321.2539232396</v>
+      </c>
+      <c r="J7" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.295671034148032</v>
+      </c>
+      <c r="L7" t="n">
+        <v>332087.9674948845</v>
+      </c>
+      <c r="M7" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N7" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1169477780071718</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1304417523926147</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1566563030223056</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.02694777800717177</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>regime_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fx_usd_to_local</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>credit_exposure</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>credit_rwa</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ccr_ead</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ccr_rwa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>cva_rwa</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>op_business_indicator</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>op_ilm</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>op_rwa</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>market_rwa</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>securitisation_rwa</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>standardised_rwa</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>modelled_rwa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>floor_applies</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>floor_factor</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>floor_add_on</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>total_rwa</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>cet1_ratio</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tier1_ratio</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>total_capital_ratio</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>leverage_ratio</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>cet1_requirement</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>cet1_surplus</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>leverage_requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Basel Framework (BCBS consolidated standards)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9625565501973241</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2048274.807488002</v>
+      </c>
+      <c r="F2" t="n">
+        <v>901803.3739777341</v>
+      </c>
+      <c r="G2" t="n">
+        <v>276492.0462706767</v>
+      </c>
+      <c r="H2" t="n">
+        <v>172165.0586869715</v>
+      </c>
+      <c r="I2" t="n">
+        <v>127321.2539232395</v>
+      </c>
+      <c r="J2" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.295601582145034</v>
+      </c>
+      <c r="L2" t="n">
+        <v>332124.599064379</v>
+      </c>
+      <c r="M2" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N2" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.1152901737067579</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1285928860575376</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.154435874673844</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.02529017370675789</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>US ERBA NPR (March 2026)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2048274.807488005</v>
+      </c>
+      <c r="F3" t="n">
+        <v>871268.6051329094</v>
+      </c>
+      <c r="G3" t="n">
+        <v>230658.8481670908</v>
+      </c>
+      <c r="H3" t="n">
+        <v>127420.2356700461</v>
+      </c>
+      <c r="I3" t="n">
+        <v>127321.2539232394</v>
+      </c>
+      <c r="J3" t="n">
+        <v>89766.66666666667</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>190350</v>
+      </c>
+      <c r="M3" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N3" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1310575395549625</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1461795633497659</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1755569022322165</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1341448928298715</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.003087353274908972</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UK PRA Basel 3.1 (PS1/26)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7981326402926173</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2048274.807488003</v>
+      </c>
+      <c r="F4" t="n">
+        <v>882671.8900404723</v>
+      </c>
+      <c r="G4" t="n">
+        <v>230658.8481670908</v>
+      </c>
+      <c r="H4" t="n">
+        <v>137790.160109282</v>
+      </c>
+      <c r="I4" t="n">
+        <v>105594.1599143253</v>
+      </c>
+      <c r="J4" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>255795.5202730408</v>
+      </c>
+      <c r="M4" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N4" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1652580.792833884</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1652580.792833884</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1258637404609531</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1403864797449092</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1685995971976717</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.03586374046095309</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EU CRR3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9625565501973241</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2042738.490596533</v>
+      </c>
+      <c r="F5" t="n">
+        <v>894273.5583173375</v>
+      </c>
+      <c r="G5" t="n">
+        <v>276492.0462706767</v>
+      </c>
+      <c r="H5" t="n">
+        <v>172165.0586869715</v>
+      </c>
+      <c r="I5" t="n">
+        <v>127321.2539232395</v>
+      </c>
+      <c r="J5" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>256347.7874999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N5" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1720836.720924312</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1720836.720924312</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1208714327575931</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1348181365373154</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1619121980723101</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.03087143275759315</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 (Singapore Basel III final reforms)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.36336509769949</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2048274.807488003</v>
+      </c>
+      <c r="F6" t="n">
+        <v>901803.3739777342</v>
+      </c>
+      <c r="G6" t="n">
+        <v>276492.0462706767</v>
+      </c>
+      <c r="H6" t="n">
+        <v>172165.0586869716</v>
+      </c>
+      <c r="I6" t="n">
+        <v>127321.2539232394</v>
+      </c>
+      <c r="J6" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.296782087274663</v>
+      </c>
+      <c r="L6" t="n">
+        <v>331502.8314298259</v>
+      </c>
+      <c r="M6" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N6" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1803521.580514534</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1803521.580514534</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1153299202223346</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.128637218709527</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1544891167473093</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.005329920222334569</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OSFI Capital Adequacy Requirements (CAR) 2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.43882953123496</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2048274.807488004</v>
+      </c>
+      <c r="F7" t="n">
+        <v>876268.2860719626</v>
+      </c>
+      <c r="G7" t="n">
+        <v>276492.0462706767</v>
+      </c>
+      <c r="H7" t="n">
+        <v>172165.0586869716</v>
+      </c>
+      <c r="I7" t="n">
+        <v>127321.2539232396</v>
+      </c>
+      <c r="J7" t="n">
+        <v>119300</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.295671034148032</v>
+      </c>
+      <c r="L7" t="n">
+        <v>332087.9674948845</v>
+      </c>
+      <c r="M7" t="n">
+        <v>205948.6017911971</v>
+      </c>
+      <c r="N7" t="n">
+        <v>64780.46070556622</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1169477780071718</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1304417523926147</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1566563030223056</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.05912372751928002</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.02694777800717177</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rwa_$M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>53022.77657932556</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>477118.3778552923</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL_RE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>74545.96985705706</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RETAIL_REGULATORY</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>29177.87530774199</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RETAIL_TRANSACTOR</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>17800.70960079274</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>COMMERCIAL_RE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>88298.59268728149</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OTHER_ASSETS</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>66156.95774213913</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>55156.76228157079</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CORPORATE_SME</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>718.5344757554336</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SPECIALISED_LENDING_PF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16919.19294874964</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>21746.98831013449</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>COVERED_BOND</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1140.636331893088</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>53022.77657932556</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>423632.3850740666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL_RE</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>74545.96985705706</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RETAIL_REGULATORY</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>29177.87530774199</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RETAIL_TRANSACTOR</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17800.70960079274</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>COMMERCIAL_RE</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>88298.5926872815</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OTHER_ASSETS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>66156.95774213913</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>71156.66355268977</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CORPORATE_SME</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>845.3346773593338</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SPECIALISED_LENDING_PF</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>17954.93972790285</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>24113.85499898246</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>COVERED_BOND</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4562.545327572354</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>53022.77657932557</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>445893.2129823593</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL_RE</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>71586.75686076617</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RETAIL_REGULATORY</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>29177.87530774199</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RETAIL_TRANSACTOR</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17800.70960079274</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>COMMERCIAL_RE</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>103351.4866192432</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OTHER_ASSETS</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>66156.95774213913</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>55156.76228157079</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CORPORATE_SME</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>718.5344757554337</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SPECIALISED_LENDING_PF</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16919.19294874965</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>13025.93358055556</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>COVERED_BOND</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1140.636331893088</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>53022.77657932556</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>471036.4445818186</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL_RE</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>71586.75686076617</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RETAIL_REGULATORY</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>29177.87530774199</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RETAIL_TRANSACTOR</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17800.70960079274</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>COMMERCIAL_RE</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>88298.59268728149</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>OTHER_ASSETS</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>66156.95774213913</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>55156.76228157079</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CORPORATE_SME</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>709.3817667554335</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SPECIALISED_LENDING_PF</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16919.19294874964</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>13025.93358055555</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>COVERED_BOND</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1140.636331893088</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>53022.77657932556</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>477118.3778552923</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL_RE</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>74545.96985705706</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RETAIL_REGULATORY</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>29177.87530774199</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RETAIL_TRANSACTOR</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17800.70960079274</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>COMMERCIAL_RE</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>88298.5926872815</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>OTHER_ASSETS</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>66156.95774213913</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>55156.76228157079</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CORPORATE_SME</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>718.5344757554337</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SPECIALISED_LENDING_PF</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>16919.19294874964</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>15932.95182374854</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>COVERED_BOND</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1140.636331893088</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>53022.77657932557</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>449107.0413367418</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL_RE</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>75881.58213794291</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RETAIL_REGULATORY</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>29177.87530774199</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RETAIL_TRANSACTOR</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>17800.70960079274</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>COMMERCIAL_RE</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>88298.5926872815</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OTHER_ASSETS</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>66156.95774213913</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>55156.76228157079</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CORPORATE_SME</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>718.5344757554337</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SPECIALISED_LENDING_PF</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>16919.19294874965</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>21746.98831013449</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>COVERED_BOND</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2281.272663786177</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>modelled_to_sa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>floor_factor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>floor_applies</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>standardised_rwa</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>modelled_rwa</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>floored_rwa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>add_on</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="G2" t="n">
+        <v>902071.6740745436</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1262900.343704361</v>
+      </c>
+      <c r="I2" t="n">
+        <v>360828.6696298174</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1082486.008889452</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1262900.343704361</v>
+      </c>
+      <c r="I3" t="n">
+        <v>180414.3348149085</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1262900.343704361</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1262900.343704361</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="G5" t="n">
+        <v>793544.578611479</v>
+      </c>
+      <c r="H5" t="n">
+        <v>793544.578611479</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="G6" t="n">
+        <v>952253.4943337748</v>
+      </c>
+      <c r="H6" t="n">
+        <v>952253.4943337748</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1110962.410056071</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1110962.410056071</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1643859.738104304</v>
+      </c>
+      <c r="G8" t="n">
+        <v>821929.8690521521</v>
+      </c>
+      <c r="H8" t="n">
+        <v>986315.8428625824</v>
+      </c>
+      <c r="I8" t="n">
+        <v>164385.9738104304</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1643859.738104304</v>
+      </c>
+      <c r="G9" t="n">
+        <v>986315.8428625825</v>
+      </c>
+      <c r="H9" t="n">
+        <v>986315.8428625826</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1643859.738104304</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1150701.816673013</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1150701.816673013</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1710595.182876365</v>
+      </c>
+      <c r="G11" t="n">
+        <v>855297.5914381823</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1026357.109725819</v>
+      </c>
+      <c r="I11" t="n">
+        <v>171059.5182876365</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1710595.182876365</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1026357.109725819</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1026357.109725819</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1710595.182876365</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1197416.628013455</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1197416.628013455</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1797707.544028149</v>
+      </c>
+      <c r="G14" t="n">
+        <v>898853.7720140743</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1168509.903618297</v>
+      </c>
+      <c r="I14" t="n">
+        <v>269656.1316042223</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1797707.544028149</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1078624.526416889</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1168509.903618297</v>
+      </c>
+      <c r="I15" t="n">
+        <v>89885.37720140751</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1797707.544028149</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1258395.280819704</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1258395.280819704</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="G17" t="n">
+        <v>889285.8143369107</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1200535.849354829</v>
+      </c>
+      <c r="I17" t="n">
+        <v>311250.0350179188</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1067142.977204293</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1200535.849354829</v>
+      </c>
+      <c r="I18" t="n">
+        <v>133392.8721505366</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1245000.140071675</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1245000.140071675</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="G20" t="n">
+        <v>902071.6740745436</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1308003.927408088</v>
+      </c>
+      <c r="I20" t="n">
+        <v>405932.2533335446</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1082486.008889452</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1308003.927408088</v>
+      </c>
+      <c r="I21" t="n">
+        <v>225517.9185186358</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1804143.348149087</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1262900.343704361</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1308003.927408088</v>
+      </c>
+      <c r="I22" t="n">
+        <v>45103.58370372729</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="G23" t="n">
+        <v>793544.578611479</v>
+      </c>
+      <c r="H23" t="n">
+        <v>793544.578611479</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="G24" t="n">
+        <v>952253.4943337748</v>
+      </c>
+      <c r="H24" t="n">
+        <v>952253.4943337748</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1587089.157222958</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1110962.410056071</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1110962.410056071</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1643859.738104304</v>
+      </c>
+      <c r="G26" t="n">
+        <v>821929.8690521521</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1191798.310125621</v>
+      </c>
+      <c r="I26" t="n">
+        <v>369868.4410734685</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1643859.738104304</v>
+      </c>
+      <c r="G27" t="n">
+        <v>986315.8428625825</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1191798.310125621</v>
+      </c>
+      <c r="I27" t="n">
+        <v>205482.467263038</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1643859.738104304</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1150701.816673013</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1191798.310125621</v>
+      </c>
+      <c r="I28" t="n">
+        <v>41096.49345260759</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1710595.182876365</v>
+      </c>
+      <c r="G29" t="n">
+        <v>855297.5914381823</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1240181.507585364</v>
+      </c>
+      <c r="I29" t="n">
+        <v>384883.9161471821</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1710595.182876365</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1026357.109725819</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1240181.507585364</v>
+      </c>
+      <c r="I30" t="n">
+        <v>213824.3978595457</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1710595.182876365</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1197416.628013455</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1240181.507585364</v>
+      </c>
+      <c r="I31" t="n">
+        <v>42764.87957190944</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1797707.544028149</v>
+      </c>
+      <c r="G32" t="n">
+        <v>898853.7720140743</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1303337.969420408</v>
+      </c>
+      <c r="I32" t="n">
+        <v>404484.1974063334</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1797707.544028149</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1078624.526416889</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1303337.969420408</v>
+      </c>
+      <c r="I33" t="n">
+        <v>224713.4430035185</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1797707.544028149</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1258395.280819704</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1303337.969420408</v>
+      </c>
+      <c r="I34" t="n">
+        <v>44942.68860070384</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="G35" t="n">
+        <v>889285.8143369107</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1200535.849354829</v>
+      </c>
+      <c r="I35" t="n">
+        <v>311250.0350179188</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1067142.977204293</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1200535.849354829</v>
+      </c>
+      <c r="I36" t="n">
+        <v>133392.8721505366</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1778571.628673821</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1245000.140071675</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1245000.140071675</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1191,7 +5125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1893,6 +5827,146 @@
       <c r="D35" t="inlineStr">
         <is>
           <t>5 in [4, 40]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>six regimes computed</t>
+        </is>
+      </c>
+      <c r="C36" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>6 in [6, 6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>US: no output floor</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0 in [0, 0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EU floor factor 2027 (Art. 465(1))</t>
+        </is>
+      </c>
+      <c r="C38" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.600 in [0.600, 0.600]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>UK floor factor 2027 (Art. 92(5))</t>
+        </is>
+      </c>
+      <c r="C39" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.600 in [0.600, 0.600]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CA floor factor (CAR Ch.1 1.5.1)</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.675 in [0.675, 0.675]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fully phased BCBS/EU/UK/SG floor 72.5%</t>
+        </is>
+      </c>
+      <c r="C41" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.725 in [0.725, 0.725]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>UK/EU op-risk ILM = 1 (UK rule 5.9; CRR Art. 312)</t>
+        </is>
+      </c>
+      <c r="C42" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.00 in [1.00, 1.00]</t>
         </is>
       </c>
     </row>
@@ -2367,7 +6441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N301"/>
+  <dimension ref="A1:P301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2441,6 +6515,16 @@
           <t>maturity</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mtm</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>collateral</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2489,6 +6573,12 @@
       <c r="N2" t="n">
         <v>3.288913527222967</v>
       </c>
+      <c r="O2" t="n">
+        <v>-12.02078174197903</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2537,6 +6627,12 @@
       <c r="N3" t="n">
         <v>2.692305325206067</v>
       </c>
+      <c r="O3" t="n">
+        <v>38.45938504524497</v>
+      </c>
+      <c r="P3" t="n">
+        <v>34.61344654072047</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2585,6 +6681,12 @@
       <c r="N4" t="n">
         <v>3.006155116018815</v>
       </c>
+      <c r="O4" t="n">
+        <v>-114.9948552722492</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2633,6 +6735,12 @@
       <c r="N5" t="n">
         <v>3.180356961271308</v>
       </c>
+      <c r="O5" t="n">
+        <v>-65.15332967194949</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2681,6 +6789,12 @@
       <c r="N6" t="n">
         <v>3.899312805205882</v>
       </c>
+      <c r="O6" t="n">
+        <v>12.22044260540287</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2729,6 +6843,12 @@
       <c r="N7" t="n">
         <v>2.566193751925947</v>
       </c>
+      <c r="O7" t="n">
+        <v>-123.8300033973247</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2777,6 +6897,12 @@
       <c r="N8" t="n">
         <v>4.285351214797934</v>
       </c>
+      <c r="O8" t="n">
+        <v>47.89671140800594</v>
+      </c>
+      <c r="P8" t="n">
+        <v>43.10704026720535</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2825,6 +6951,12 @@
       <c r="N9" t="n">
         <v>4.757506530709989</v>
       </c>
+      <c r="O9" t="n">
+        <v>-46.0476843636661</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2873,6 +7005,12 @@
       <c r="N10" t="n">
         <v>1.937224615047514</v>
       </c>
+      <c r="O10" t="n">
+        <v>72.50398454632521</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2921,6 +7059,12 @@
       <c r="N11" t="n">
         <v>3.960212205780167</v>
       </c>
+      <c r="O11" t="n">
+        <v>35.54330504358497</v>
+      </c>
+      <c r="P11" t="n">
+        <v>31.98897453922648</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2969,6 +7113,12 @@
       <c r="N12" t="n">
         <v>4.557098329664518</v>
       </c>
+      <c r="O12" t="n">
+        <v>-155.3335485598873</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3017,6 +7167,12 @@
       <c r="N13" t="n">
         <v>2.308773128914387</v>
       </c>
+      <c r="O13" t="n">
+        <v>121.5031451007841</v>
+      </c>
+      <c r="P13" t="n">
+        <v>109.3528305907057</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3065,6 +7221,12 @@
       <c r="N14" t="n">
         <v>3.064250425338022</v>
       </c>
+      <c r="O14" t="n">
+        <v>9.99242527072575</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8.993182743653175</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3113,6 +7275,12 @@
       <c r="N15" t="n">
         <v>3.645928239001293</v>
       </c>
+      <c r="O15" t="n">
+        <v>-520.535644537029</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3161,6 +7329,12 @@
       <c r="N16" t="n">
         <v>3.672894884679673</v>
       </c>
+      <c r="O16" t="n">
+        <v>-22.77791908358246</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3209,6 +7383,12 @@
       <c r="N17" t="n">
         <v>1.975657137667874</v>
       </c>
+      <c r="O17" t="n">
+        <v>-18.7965371427829</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3257,6 +7437,12 @@
       <c r="N18" t="n">
         <v>2.556479828863465</v>
       </c>
+      <c r="O18" t="n">
+        <v>29.8364548160871</v>
+      </c>
+      <c r="P18" t="n">
+        <v>26.85280933447839</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3305,6 +7491,12 @@
       <c r="N19" t="n">
         <v>3.604879276144166</v>
       </c>
+      <c r="O19" t="n">
+        <v>-57.87982504276405</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3353,6 +7545,12 @@
       <c r="N20" t="n">
         <v>4.936715544469548</v>
       </c>
+      <c r="O20" t="n">
+        <v>-117.8134352970403</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3401,6 +7599,12 @@
       <c r="N21" t="n">
         <v>3.124760976784627</v>
       </c>
+      <c r="O21" t="n">
+        <v>-39.73159530787699</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3449,6 +7653,12 @@
       <c r="N22" t="n">
         <v>2.120636460777931</v>
       </c>
+      <c r="O22" t="n">
+        <v>110.8601856875372</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3497,6 +7707,12 @@
       <c r="N23" t="n">
         <v>4.659479297943093</v>
       </c>
+      <c r="O23" t="n">
+        <v>-135.6012476340477</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3545,6 +7761,12 @@
       <c r="N24" t="n">
         <v>3.208224838150008</v>
       </c>
+      <c r="O24" t="n">
+        <v>5.302195674720416</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3593,6 +7815,12 @@
       <c r="N25" t="n">
         <v>2.711961176466903</v>
       </c>
+      <c r="O25" t="n">
+        <v>-81.39344775244638</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3641,6 +7869,12 @@
       <c r="N26" t="n">
         <v>5.653529374892787</v>
       </c>
+      <c r="O26" t="n">
+        <v>34.13846248714827</v>
+      </c>
+      <c r="P26" t="n">
+        <v>30.72461623843344</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3689,6 +7923,12 @@
       <c r="N27" t="n">
         <v>3.968277100781557</v>
       </c>
+      <c r="O27" t="n">
+        <v>-65.04439671805615</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3737,6 +7977,12 @@
       <c r="N28" t="n">
         <v>3.356196446770658</v>
       </c>
+      <c r="O28" t="n">
+        <v>104.7279824585327</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3785,6 +8031,12 @@
       <c r="N29" t="n">
         <v>4.546527169434617</v>
       </c>
+      <c r="O29" t="n">
+        <v>55.31532952817207</v>
+      </c>
+      <c r="P29" t="n">
+        <v>49.78379657535486</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3833,6 +8085,12 @@
       <c r="N30" t="n">
         <v>1.918962421756294</v>
       </c>
+      <c r="O30" t="n">
+        <v>-30.66954523485384</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3881,6 +8139,12 @@
       <c r="N31" t="n">
         <v>4.206325829864586</v>
       </c>
+      <c r="O31" t="n">
+        <v>33.70203402907781</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3929,6 +8193,12 @@
       <c r="N32" t="n">
         <v>4.915471259874509</v>
       </c>
+      <c r="O32" t="n">
+        <v>-173.8149327736435</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3977,6 +8247,12 @@
       <c r="N33" t="n">
         <v>2.823041193053096</v>
       </c>
+      <c r="O33" t="n">
+        <v>5.399397660700145</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4025,6 +8301,12 @@
       <c r="N34" t="n">
         <v>2.283771943643341</v>
       </c>
+      <c r="O34" t="n">
+        <v>-38.67504153078706</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4073,6 +8355,12 @@
       <c r="N35" t="n">
         <v>2.240659458043229</v>
       </c>
+      <c r="O35" t="n">
+        <v>-32.14547125462718</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4121,6 +8409,12 @@
       <c r="N36" t="n">
         <v>3.047968204716232</v>
       </c>
+      <c r="O36" t="n">
+        <v>-34.62690042474516</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4169,6 +8463,12 @@
       <c r="N37" t="n">
         <v>3.93855305275388</v>
       </c>
+      <c r="O37" t="n">
+        <v>-3.565853561288711</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4217,6 +8517,12 @@
       <c r="N38" t="n">
         <v>8.183670256027627</v>
       </c>
+      <c r="O38" t="n">
+        <v>19.29554683822675</v>
+      </c>
+      <c r="P38" t="n">
+        <v>17.36599215440408</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4265,6 +8571,12 @@
       <c r="N39" t="n">
         <v>4.082443449049069</v>
       </c>
+      <c r="O39" t="n">
+        <v>146.5294263707735</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4313,6 +8625,12 @@
       <c r="N40" t="n">
         <v>6.059641605934128</v>
       </c>
+      <c r="O40" t="n">
+        <v>-4.940163358340612</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4361,6 +8679,12 @@
       <c r="N41" t="n">
         <v>6.477766207129961</v>
       </c>
+      <c r="O41" t="n">
+        <v>-41.09236234002979</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4409,6 +8733,12 @@
       <c r="N42" t="n">
         <v>6.25372290385979</v>
       </c>
+      <c r="O42" t="n">
+        <v>11.0159784226702</v>
+      </c>
+      <c r="P42" t="n">
+        <v>9.914380580403179</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4457,6 +8787,12 @@
       <c r="N43" t="n">
         <v>2.869861860953048</v>
       </c>
+      <c r="O43" t="n">
+        <v>-24.39153007310017</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4505,6 +8841,12 @@
       <c r="N44" t="n">
         <v>2.282065627568341</v>
       </c>
+      <c r="O44" t="n">
+        <v>151.2724163889293</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4553,6 +8895,12 @@
       <c r="N45" t="n">
         <v>2.896526872339867</v>
       </c>
+      <c r="O45" t="n">
+        <v>32.98818920762536</v>
+      </c>
+      <c r="P45" t="n">
+        <v>29.68937028686283</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4601,6 +8949,12 @@
       <c r="N46" t="n">
         <v>2.255342940620143</v>
       </c>
+      <c r="O46" t="n">
+        <v>-21.03118459592999</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4649,6 +9003,12 @@
       <c r="N47" t="n">
         <v>4.840189525395302</v>
       </c>
+      <c r="O47" t="n">
+        <v>-30.20240316736709</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4697,6 +9057,12 @@
       <c r="N48" t="n">
         <v>10.59484839694719</v>
       </c>
+      <c r="O48" t="n">
+        <v>54.08178684947742</v>
+      </c>
+      <c r="P48" t="n">
+        <v>48.67360816452967</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4745,6 +9111,12 @@
       <c r="N49" t="n">
         <v>2.274684151250718</v>
       </c>
+      <c r="O49" t="n">
+        <v>-100.2666888376489</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4793,6 +9165,12 @@
       <c r="N50" t="n">
         <v>5.506777663999283</v>
       </c>
+      <c r="O50" t="n">
+        <v>89.22039704846975</v>
+      </c>
+      <c r="P50" t="n">
+        <v>80.29835734362278</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4841,6 +9219,12 @@
       <c r="N51" t="n">
         <v>2.742695648518363</v>
       </c>
+      <c r="O51" t="n">
+        <v>26.55341395108938</v>
+      </c>
+      <c r="P51" t="n">
+        <v>23.89807255598044</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4889,6 +9273,12 @@
       <c r="N52" t="n">
         <v>4.271461591083504</v>
       </c>
+      <c r="O52" t="n">
+        <v>91.71948049051372</v>
+      </c>
+      <c r="P52" t="n">
+        <v>82.54753244146235</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4937,6 +9327,12 @@
       <c r="N53" t="n">
         <v>3.882850853634516</v>
       </c>
+      <c r="O53" t="n">
+        <v>-72.53745715953822</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4985,6 +9381,12 @@
       <c r="N54" t="n">
         <v>2.117622663784005</v>
       </c>
+      <c r="O54" t="n">
+        <v>24.46554194255101</v>
+      </c>
+      <c r="P54" t="n">
+        <v>22.01898774829591</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5033,6 +9435,12 @@
       <c r="N55" t="n">
         <v>3.340687111521174</v>
       </c>
+      <c r="O55" t="n">
+        <v>-65.49521711034653</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5081,6 +9489,12 @@
       <c r="N56" t="n">
         <v>4.273395701028222</v>
       </c>
+      <c r="O56" t="n">
+        <v>-42.41826789512886</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5129,6 +9543,12 @@
       <c r="N57" t="n">
         <v>3.475590113731061</v>
       </c>
+      <c r="O57" t="n">
+        <v>24.42952904459739</v>
+      </c>
+      <c r="P57" t="n">
+        <v>21.98657614013765</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5177,6 +9597,12 @@
       <c r="N58" t="n">
         <v>8.661400558681796</v>
       </c>
+      <c r="O58" t="n">
+        <v>-52.22303528919144</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5225,6 +9651,12 @@
       <c r="N59" t="n">
         <v>8.479394769514451</v>
       </c>
+      <c r="O59" t="n">
+        <v>-391.9431183595883</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5273,6 +9705,12 @@
       <c r="N60" t="n">
         <v>2.315374970708626</v>
       </c>
+      <c r="O60" t="n">
+        <v>43.3515787786096</v>
+      </c>
+      <c r="P60" t="n">
+        <v>39.01642090074864</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5321,6 +9759,12 @@
       <c r="N61" t="n">
         <v>2.646173882960951</v>
       </c>
+      <c r="O61" t="n">
+        <v>-34.48047418797393</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5369,6 +9813,12 @@
       <c r="N62" t="n">
         <v>3.417442848881417</v>
       </c>
+      <c r="O62" t="n">
+        <v>0.8782593991091951</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5417,6 +9867,12 @@
       <c r="N63" t="n">
         <v>5.344657829409095</v>
       </c>
+      <c r="O63" t="n">
+        <v>-47.89804350252474</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5465,6 +9921,12 @@
       <c r="N64" t="n">
         <v>3.993417719438788</v>
       </c>
+      <c r="O64" t="n">
+        <v>-9.373055771244207</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5513,6 +9975,12 @@
       <c r="N65" t="n">
         <v>3.310065870514597</v>
       </c>
+      <c r="O65" t="n">
+        <v>130.1518754188702</v>
+      </c>
+      <c r="P65" t="n">
+        <v>117.1366878769832</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5561,6 +10029,12 @@
       <c r="N66" t="n">
         <v>2.558333195238999</v>
       </c>
+      <c r="O66" t="n">
+        <v>-8.540115234180265</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5609,6 +10083,12 @@
       <c r="N67" t="n">
         <v>5.390505873609701</v>
       </c>
+      <c r="O67" t="n">
+        <v>-62.29556448506045</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5657,6 +10137,12 @@
       <c r="N68" t="n">
         <v>6.343331315335969</v>
       </c>
+      <c r="O68" t="n">
+        <v>164.514872503812</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5705,6 +10191,12 @@
       <c r="N69" t="n">
         <v>1.607402769748294</v>
       </c>
+      <c r="O69" t="n">
+        <v>6.23811595665644</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5753,6 +10245,12 @@
       <c r="N70" t="n">
         <v>3.54137366373867</v>
       </c>
+      <c r="O70" t="n">
+        <v>-59.8933918628621</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5801,6 +10299,12 @@
       <c r="N71" t="n">
         <v>3.246035200937242</v>
       </c>
+      <c r="O71" t="n">
+        <v>47.50107204381863</v>
+      </c>
+      <c r="P71" t="n">
+        <v>42.75096483943677</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5849,6 +10353,12 @@
       <c r="N72" t="n">
         <v>3.865499411263872</v>
       </c>
+      <c r="O72" t="n">
+        <v>28.52779978497083</v>
+      </c>
+      <c r="P72" t="n">
+        <v>25.67501980647375</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5897,6 +10407,12 @@
       <c r="N73" t="n">
         <v>4.217136222814691</v>
       </c>
+      <c r="O73" t="n">
+        <v>52.31036155970053</v>
+      </c>
+      <c r="P73" t="n">
+        <v>47.07932540373048</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5945,6 +10461,12 @@
       <c r="N74" t="n">
         <v>1.791977841629442</v>
       </c>
+      <c r="O74" t="n">
+        <v>-44.92298366159171</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5993,6 +10515,12 @@
       <c r="N75" t="n">
         <v>2.251332515415074</v>
       </c>
+      <c r="O75" t="n">
+        <v>-132.6107569560072</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6041,6 +10569,12 @@
       <c r="N76" t="n">
         <v>2.807537733540269</v>
       </c>
+      <c r="O76" t="n">
+        <v>-35.14917294959847</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6089,6 +10623,12 @@
       <c r="N77" t="n">
         <v>3.234255848932219</v>
       </c>
+      <c r="O77" t="n">
+        <v>95.56017474368927</v>
+      </c>
+      <c r="P77" t="n">
+        <v>86.00415726932034</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6137,6 +10677,12 @@
       <c r="N78" t="n">
         <v>3.552897718727882</v>
       </c>
+      <c r="O78" t="n">
+        <v>192.5210342187768</v>
+      </c>
+      <c r="P78" t="n">
+        <v>173.2689307968991</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6185,6 +10731,12 @@
       <c r="N79" t="n">
         <v>3.015185402515774</v>
       </c>
+      <c r="O79" t="n">
+        <v>-160.850692992975</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6233,6 +10785,12 @@
       <c r="N80" t="n">
         <v>3.386654379582656</v>
       </c>
+      <c r="O80" t="n">
+        <v>-150.0101655625321</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6281,6 +10839,12 @@
       <c r="N81" t="n">
         <v>2.606351896875828</v>
       </c>
+      <c r="O81" t="n">
+        <v>-121.269943927576</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6329,6 +10893,12 @@
       <c r="N82" t="n">
         <v>4.193812900089418</v>
       </c>
+      <c r="O82" t="n">
+        <v>-4.740102437446012</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6377,6 +10947,12 @@
       <c r="N83" t="n">
         <v>2.841110160179513</v>
       </c>
+      <c r="O83" t="n">
+        <v>55.67685500974002</v>
+      </c>
+      <c r="P83" t="n">
+        <v>50.10916950876602</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6425,6 +11001,12 @@
       <c r="N84" t="n">
         <v>2.884706431324407</v>
       </c>
+      <c r="O84" t="n">
+        <v>22.09829535646515</v>
+      </c>
+      <c r="P84" t="n">
+        <v>19.88846582081864</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6473,6 +11055,12 @@
       <c r="N85" t="n">
         <v>2.648233630875368</v>
       </c>
+      <c r="O85" t="n">
+        <v>55.7384616267804</v>
+      </c>
+      <c r="P85" t="n">
+        <v>50.16461546410236</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6521,6 +11109,12 @@
       <c r="N86" t="n">
         <v>3.545594253861634</v>
       </c>
+      <c r="O86" t="n">
+        <v>-0.4380664856568591</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6569,6 +11163,12 @@
       <c r="N87" t="n">
         <v>6.284181319989787</v>
       </c>
+      <c r="O87" t="n">
+        <v>59.07144981246091</v>
+      </c>
+      <c r="P87" t="n">
+        <v>53.16430483121482</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6617,6 +11217,12 @@
       <c r="N88" t="n">
         <v>4.968830465782867</v>
       </c>
+      <c r="O88" t="n">
+        <v>57.79544943166208</v>
+      </c>
+      <c r="P88" t="n">
+        <v>52.01590448849587</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6665,6 +11271,12 @@
       <c r="N89" t="n">
         <v>3.824535815003765</v>
       </c>
+      <c r="O89" t="n">
+        <v>-44.15101189015079</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6713,6 +11325,12 @@
       <c r="N90" t="n">
         <v>3.201841991937757</v>
       </c>
+      <c r="O90" t="n">
+        <v>-17.83974582413593</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6761,6 +11379,12 @@
       <c r="N91" t="n">
         <v>1.225413418214124</v>
       </c>
+      <c r="O91" t="n">
+        <v>-81.01357879832047</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6809,6 +11433,12 @@
       <c r="N92" t="n">
         <v>3.58919760890164</v>
       </c>
+      <c r="O92" t="n">
+        <v>-1.648783335051913</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6857,6 +11487,12 @@
       <c r="N93" t="n">
         <v>2.969844656522879</v>
       </c>
+      <c r="O93" t="n">
+        <v>41.20877061633475</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6905,6 +11541,12 @@
       <c r="N94" t="n">
         <v>6.376868158663211</v>
       </c>
+      <c r="O94" t="n">
+        <v>51.93924094469585</v>
+      </c>
+      <c r="P94" t="n">
+        <v>46.74531685022627</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6953,6 +11595,12 @@
       <c r="N95" t="n">
         <v>3.028665727440051</v>
       </c>
+      <c r="O95" t="n">
+        <v>-61.39464073908972</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7001,6 +11649,12 @@
       <c r="N96" t="n">
         <v>4.025378768720905</v>
       </c>
+      <c r="O96" t="n">
+        <v>-85.46794338786582</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7049,6 +11703,12 @@
       <c r="N97" t="n">
         <v>5.030982921472789</v>
       </c>
+      <c r="O97" t="n">
+        <v>10.37604870883661</v>
+      </c>
+      <c r="P97" t="n">
+        <v>9.338443837952953</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7097,6 +11757,12 @@
       <c r="N98" t="n">
         <v>10.90335201481532</v>
       </c>
+      <c r="O98" t="n">
+        <v>-6.825248149586411</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7145,6 +11811,12 @@
       <c r="N99" t="n">
         <v>2.504641167749347</v>
       </c>
+      <c r="O99" t="n">
+        <v>16.11368636895084</v>
+      </c>
+      <c r="P99" t="n">
+        <v>14.50231773205576</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7193,6 +11865,12 @@
       <c r="N100" t="n">
         <v>2.928864993361439</v>
       </c>
+      <c r="O100" t="n">
+        <v>32.55624246732278</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7241,6 +11919,12 @@
       <c r="N101" t="n">
         <v>2.138586758384419</v>
       </c>
+      <c r="O101" t="n">
+        <v>-90.54411828453135</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7289,6 +11973,12 @@
       <c r="N102" t="n">
         <v>3.703305021701416</v>
       </c>
+      <c r="O102" t="n">
+        <v>110.7964300292211</v>
+      </c>
+      <c r="P102" t="n">
+        <v>99.71678702629897</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7337,6 +12027,12 @@
       <c r="N103" t="n">
         <v>3.841986070354285</v>
       </c>
+      <c r="O103" t="n">
+        <v>96.22665135898978</v>
+      </c>
+      <c r="P103" t="n">
+        <v>86.60398622309081</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7385,6 +12081,12 @@
       <c r="N104" t="n">
         <v>3.172359739792308</v>
       </c>
+      <c r="O104" t="n">
+        <v>-13.02790109128381</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7433,6 +12135,12 @@
       <c r="N105" t="n">
         <v>2.226993533291898</v>
       </c>
+      <c r="O105" t="n">
+        <v>137.5554551874626</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7481,6 +12189,12 @@
       <c r="N106" t="n">
         <v>4.4217350808324</v>
       </c>
+      <c r="O106" t="n">
+        <v>-55.73020899002555</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7529,6 +12243,12 @@
       <c r="N107" t="n">
         <v>2.417215595368516</v>
       </c>
+      <c r="O107" t="n">
+        <v>-20.53867517293111</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7577,6 +12297,12 @@
       <c r="N108" t="n">
         <v>2.187122850012468</v>
       </c>
+      <c r="O108" t="n">
+        <v>113.5727429450175</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7625,6 +12351,12 @@
       <c r="N109" t="n">
         <v>2.794723372459495</v>
       </c>
+      <c r="O109" t="n">
+        <v>12.20717053978495</v>
+      </c>
+      <c r="P109" t="n">
+        <v>10.98645348580645</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7673,6 +12405,12 @@
       <c r="N110" t="n">
         <v>5.232516771110284</v>
       </c>
+      <c r="O110" t="n">
+        <v>224.3383208817481</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7721,6 +12459,12 @@
       <c r="N111" t="n">
         <v>6.525258177952185</v>
       </c>
+      <c r="O111" t="n">
+        <v>82.3716229275748</v>
+      </c>
+      <c r="P111" t="n">
+        <v>74.13446063481733</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7769,6 +12513,12 @@
       <c r="N112" t="n">
         <v>4.279951433977926</v>
       </c>
+      <c r="O112" t="n">
+        <v>-31.97115543479852</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7817,6 +12567,12 @@
       <c r="N113" t="n">
         <v>5.843055038830809</v>
       </c>
+      <c r="O113" t="n">
+        <v>-94.60488727192975</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7865,6 +12621,12 @@
       <c r="N114" t="n">
         <v>2.835789589169312</v>
       </c>
+      <c r="O114" t="n">
+        <v>55.54958816511601</v>
+      </c>
+      <c r="P114" t="n">
+        <v>49.99462934860441</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7913,6 +12675,12 @@
       <c r="N115" t="n">
         <v>3.359966653591786</v>
       </c>
+      <c r="O115" t="n">
+        <v>44.23561052473512</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7961,6 +12729,12 @@
       <c r="N116" t="n">
         <v>5.032171127650237</v>
       </c>
+      <c r="O116" t="n">
+        <v>-35.22159446147819</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8009,6 +12783,12 @@
       <c r="N117" t="n">
         <v>2.64771314480958</v>
       </c>
+      <c r="O117" t="n">
+        <v>80.6514792456565</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8057,6 +12837,12 @@
       <c r="N118" t="n">
         <v>2.532991332293499</v>
       </c>
+      <c r="O118" t="n">
+        <v>-75.40022726866023</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8105,6 +12891,12 @@
       <c r="N119" t="n">
         <v>1.295736918748628</v>
       </c>
+      <c r="O119" t="n">
+        <v>-114.1921687942388</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8153,6 +12945,12 @@
       <c r="N120" t="n">
         <v>6.073416784262328</v>
       </c>
+      <c r="O120" t="n">
+        <v>50.59459911938488</v>
+      </c>
+      <c r="P120" t="n">
+        <v>45.53513920744639</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8201,6 +12999,12 @@
       <c r="N121" t="n">
         <v>4.113566862166681</v>
       </c>
+      <c r="O121" t="n">
+        <v>24.78811296330858</v>
+      </c>
+      <c r="P121" t="n">
+        <v>22.30930166697773</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8249,6 +13053,12 @@
       <c r="N122" t="n">
         <v>4.78885648912459</v>
       </c>
+      <c r="O122" t="n">
+        <v>34.5718568065578</v>
+      </c>
+      <c r="P122" t="n">
+        <v>31.11467112590202</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8297,6 +13107,12 @@
       <c r="N123" t="n">
         <v>5.229693174824779</v>
       </c>
+      <c r="O123" t="n">
+        <v>311.6352854585417</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8345,6 +13161,12 @@
       <c r="N124" t="n">
         <v>2.591350974244834</v>
       </c>
+      <c r="O124" t="n">
+        <v>-40.31051154332629</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8393,6 +13215,12 @@
       <c r="N125" t="n">
         <v>1.83643328111709</v>
       </c>
+      <c r="O125" t="n">
+        <v>111.22888784089</v>
+      </c>
+      <c r="P125" t="n">
+        <v>100.105999056801</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8441,6 +13269,12 @@
       <c r="N126" t="n">
         <v>2.234690872642985</v>
       </c>
+      <c r="O126" t="n">
+        <v>88.14919496289549</v>
+      </c>
+      <c r="P126" t="n">
+        <v>79.33427546660594</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8489,6 +13323,12 @@
       <c r="N127" t="n">
         <v>2.001729169128198</v>
       </c>
+      <c r="O127" t="n">
+        <v>10.14832416601703</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8537,6 +13377,12 @@
       <c r="N128" t="n">
         <v>2.555542835255962</v>
       </c>
+      <c r="O128" t="n">
+        <v>-96.24823443716004</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8585,6 +13431,12 @@
       <c r="N129" t="n">
         <v>2.415965297440544</v>
       </c>
+      <c r="O129" t="n">
+        <v>191.1357455550894</v>
+      </c>
+      <c r="P129" t="n">
+        <v>172.0221709995805</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8633,6 +13485,12 @@
       <c r="N130" t="n">
         <v>1.897754180048987</v>
       </c>
+      <c r="O130" t="n">
+        <v>-39.47254782333678</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8681,6 +13539,12 @@
       <c r="N131" t="n">
         <v>2.723035227523345</v>
       </c>
+      <c r="O131" t="n">
+        <v>24.20904527652321</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8729,6 +13593,12 @@
       <c r="N132" t="n">
         <v>3.920360620180794</v>
       </c>
+      <c r="O132" t="n">
+        <v>-176.6933497963515</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8777,6 +13647,12 @@
       <c r="N133" t="n">
         <v>2.940868018247802</v>
       </c>
+      <c r="O133" t="n">
+        <v>-33.65489163292425</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8825,6 +13701,12 @@
       <c r="N134" t="n">
         <v>3.67966809601763</v>
       </c>
+      <c r="O134" t="n">
+        <v>-37.42888843718943</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8873,6 +13755,12 @@
       <c r="N135" t="n">
         <v>2.827548725356243</v>
       </c>
+      <c r="O135" t="n">
+        <v>-104.0627689245887</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8921,6 +13809,12 @@
       <c r="N136" t="n">
         <v>4.605123588631288</v>
       </c>
+      <c r="O136" t="n">
+        <v>6.685573491539342</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8969,6 +13863,12 @@
       <c r="N137" t="n">
         <v>2.467027617765636</v>
       </c>
+      <c r="O137" t="n">
+        <v>66.30761572545222</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9017,6 +13917,12 @@
       <c r="N138" t="n">
         <v>7.844814409226149</v>
       </c>
+      <c r="O138" t="n">
+        <v>-145.5151536124113</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9065,6 +13971,12 @@
       <c r="N139" t="n">
         <v>2.370927516134116</v>
       </c>
+      <c r="O139" t="n">
+        <v>-280.3629348166241</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9113,6 +14025,12 @@
       <c r="N140" t="n">
         <v>10.06811795593902</v>
       </c>
+      <c r="O140" t="n">
+        <v>-125.2910313217201</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9161,6 +14079,12 @@
       <c r="N141" t="n">
         <v>4.425658303340938</v>
       </c>
+      <c r="O141" t="n">
+        <v>-46.99631637317441</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9209,6 +14133,12 @@
       <c r="N142" t="n">
         <v>2.55930809130073</v>
       </c>
+      <c r="O142" t="n">
+        <v>-146.3319437577487</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9257,6 +14187,12 @@
       <c r="N143" t="n">
         <v>3.625881292609194</v>
       </c>
+      <c r="O143" t="n">
+        <v>4.332941224323925</v>
+      </c>
+      <c r="P143" t="n">
+        <v>3.899647101891532</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9305,6 +14241,12 @@
       <c r="N144" t="n">
         <v>1.278303041097141</v>
       </c>
+      <c r="O144" t="n">
+        <v>-71.65562782716711</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9353,6 +14295,12 @@
       <c r="N145" t="n">
         <v>3.86084332283084</v>
       </c>
+      <c r="O145" t="n">
+        <v>-16.22857124011804</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9401,6 +14349,12 @@
       <c r="N146" t="n">
         <v>3.698248914682159</v>
       </c>
+      <c r="O146" t="n">
+        <v>-22.79115770762833</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9449,6 +14403,12 @@
       <c r="N147" t="n">
         <v>4.716477160598726</v>
       </c>
+      <c r="O147" t="n">
+        <v>-46.3845649977164</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9497,6 +14457,12 @@
       <c r="N148" t="n">
         <v>2.456255987664237</v>
       </c>
+      <c r="O148" t="n">
+        <v>171.5259438527638</v>
+      </c>
+      <c r="P148" t="n">
+        <v>154.3733494674875</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9545,6 +14511,12 @@
       <c r="N149" t="n">
         <v>3.738281378261603</v>
       </c>
+      <c r="O149" t="n">
+        <v>56.91985255362772</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9593,6 +14565,12 @@
       <c r="N150" t="n">
         <v>5.284528077178751</v>
       </c>
+      <c r="O150" t="n">
+        <v>-85.63922504244353</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9641,6 +14619,12 @@
       <c r="N151" t="n">
         <v>4.370934888850453</v>
       </c>
+      <c r="O151" t="n">
+        <v>54.98766481416862</v>
+      </c>
+      <c r="P151" t="n">
+        <v>49.48889833275177</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9689,6 +14673,12 @@
       <c r="N152" t="n">
         <v>4.125412591443242</v>
       </c>
+      <c r="O152" t="n">
+        <v>101.7356601251337</v>
+      </c>
+      <c r="P152" t="n">
+        <v>91.5620941126203</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9737,6 +14727,12 @@
       <c r="N153" t="n">
         <v>2.476639034380873</v>
       </c>
+      <c r="O153" t="n">
+        <v>23.92425316233641</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9785,6 +14781,12 @@
       <c r="N154" t="n">
         <v>4.411551450764761</v>
       </c>
+      <c r="O154" t="n">
+        <v>-62.73703183174747</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9833,6 +14835,12 @@
       <c r="N155" t="n">
         <v>2.53920334912131</v>
       </c>
+      <c r="O155" t="n">
+        <v>-139.2723429008046</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9881,6 +14889,12 @@
       <c r="N156" t="n">
         <v>2.124423048618916</v>
       </c>
+      <c r="O156" t="n">
+        <v>96.84389725610349</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9929,6 +14943,12 @@
       <c r="N157" t="n">
         <v>2.503985242530106</v>
       </c>
+      <c r="O157" t="n">
+        <v>-78.55680923145727</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9977,6 +14997,12 @@
       <c r="N158" t="n">
         <v>2.785566312983737</v>
       </c>
+      <c r="O158" t="n">
+        <v>-69.03011334550135</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10025,6 +15051,12 @@
       <c r="N159" t="n">
         <v>4.834793935900372</v>
       </c>
+      <c r="O159" t="n">
+        <v>-0.8121136510946929</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10073,6 +15105,12 @@
       <c r="N160" t="n">
         <v>1.543477291926529</v>
       </c>
+      <c r="O160" t="n">
+        <v>-32.34202842640936</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10121,6 +15159,12 @@
       <c r="N161" t="n">
         <v>2.336970943276321</v>
       </c>
+      <c r="O161" t="n">
+        <v>63.96349650244363</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10169,6 +15213,12 @@
       <c r="N162" t="n">
         <v>1.436756999592483</v>
       </c>
+      <c r="O162" t="n">
+        <v>-43.07029148965414</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10217,6 +15267,12 @@
       <c r="N163" t="n">
         <v>6.34114938290056</v>
       </c>
+      <c r="O163" t="n">
+        <v>-170.6373604807169</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10265,6 +15321,12 @@
       <c r="N164" t="n">
         <v>3.920179502570965</v>
       </c>
+      <c r="O164" t="n">
+        <v>-13.31301539201979</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10313,6 +15375,12 @@
       <c r="N165" t="n">
         <v>3.242732599896235</v>
       </c>
+      <c r="O165" t="n">
+        <v>43.13807166168392</v>
+      </c>
+      <c r="P165" t="n">
+        <v>38.82426449551554</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10361,6 +15429,12 @@
       <c r="N166" t="n">
         <v>2.371665644213808</v>
       </c>
+      <c r="O166" t="n">
+        <v>95.30771435008094</v>
+      </c>
+      <c r="P166" t="n">
+        <v>85.77694291507285</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10409,6 +15483,12 @@
       <c r="N167" t="n">
         <v>3.529445061230215</v>
       </c>
+      <c r="O167" t="n">
+        <v>6.206647639151378</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10457,6 +15537,12 @@
       <c r="N168" t="n">
         <v>2.410129727228563</v>
       </c>
+      <c r="O168" t="n">
+        <v>-26.02628016724136</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10505,6 +15591,12 @@
       <c r="N169" t="n">
         <v>2.233373530683551</v>
       </c>
+      <c r="O169" t="n">
+        <v>112.8547890429584</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10553,6 +15645,12 @@
       <c r="N170" t="n">
         <v>5.603579326606587</v>
       </c>
+      <c r="O170" t="n">
+        <v>12.82289216798942</v>
+      </c>
+      <c r="P170" t="n">
+        <v>11.54060295119048</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10601,6 +15699,12 @@
       <c r="N171" t="n">
         <v>1.801096639845203</v>
       </c>
+      <c r="O171" t="n">
+        <v>98.80098912371332</v>
+      </c>
+      <c r="P171" t="n">
+        <v>88.920890211342</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10649,6 +15753,12 @@
       <c r="N172" t="n">
         <v>1.449829219329079</v>
       </c>
+      <c r="O172" t="n">
+        <v>-55.5744163224134</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10697,6 +15807,12 @@
       <c r="N173" t="n">
         <v>2.497327815746071</v>
       </c>
+      <c r="O173" t="n">
+        <v>-199.3235018859245</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10745,6 +15861,12 @@
       <c r="N174" t="n">
         <v>4.855052860664737</v>
       </c>
+      <c r="O174" t="n">
+        <v>76.77149011796986</v>
+      </c>
+      <c r="P174" t="n">
+        <v>69.09434110617288</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10793,6 +15915,12 @@
       <c r="N175" t="n">
         <v>2.158214830976116</v>
       </c>
+      <c r="O175" t="n">
+        <v>-288.6796147651568</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10841,6 +15969,12 @@
       <c r="N176" t="n">
         <v>2.04960324861062</v>
       </c>
+      <c r="O176" t="n">
+        <v>19.5478549830159</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10889,6 +16023,12 @@
       <c r="N177" t="n">
         <v>2.727531300628852</v>
       </c>
+      <c r="O177" t="n">
+        <v>44.26113416050123</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10937,6 +16077,12 @@
       <c r="N178" t="n">
         <v>4.477402665749851</v>
       </c>
+      <c r="O178" t="n">
+        <v>-56.4372339474812</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10985,6 +16131,12 @@
       <c r="N179" t="n">
         <v>4.216005294026916</v>
       </c>
+      <c r="O179" t="n">
+        <v>-145.2116492553892</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11033,6 +16185,12 @@
       <c r="N180" t="n">
         <v>4.942251237848378</v>
       </c>
+      <c r="O180" t="n">
+        <v>139.1888181228428</v>
+      </c>
+      <c r="P180" t="n">
+        <v>125.2699363105585</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11081,6 +16239,12 @@
       <c r="N181" t="n">
         <v>3.018250502695603</v>
       </c>
+      <c r="O181" t="n">
+        <v>357.2748345032171</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11129,6 +16293,12 @@
       <c r="N182" t="n">
         <v>3.303083117857902</v>
       </c>
+      <c r="O182" t="n">
+        <v>22.07757457710364</v>
+      </c>
+      <c r="P182" t="n">
+        <v>19.86981711939328</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11177,6 +16347,12 @@
       <c r="N183" t="n">
         <v>2.493168095750111</v>
       </c>
+      <c r="O183" t="n">
+        <v>-82.74610607358794</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11225,6 +16401,12 @@
       <c r="N184" t="n">
         <v>3.365100900270126</v>
       </c>
+      <c r="O184" t="n">
+        <v>-67.74318742416941</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11273,6 +16455,12 @@
       <c r="N185" t="n">
         <v>6.713435295390899</v>
       </c>
+      <c r="O185" t="n">
+        <v>-144.4210344592489</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11321,6 +16509,12 @@
       <c r="N186" t="n">
         <v>2.495437162974165</v>
       </c>
+      <c r="O186" t="n">
+        <v>222.0355336156032</v>
+      </c>
+      <c r="P186" t="n">
+        <v>199.8319802540429</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11369,6 +16563,12 @@
       <c r="N187" t="n">
         <v>1.812145631599992</v>
       </c>
+      <c r="O187" t="n">
+        <v>-8.606750660338371</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11417,6 +16617,12 @@
       <c r="N188" t="n">
         <v>7.2511618475644</v>
       </c>
+      <c r="O188" t="n">
+        <v>-61.22092557767822</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11465,6 +16671,12 @@
       <c r="N189" t="n">
         <v>1.317498403710253</v>
       </c>
+      <c r="O189" t="n">
+        <v>17.41202776200835</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11513,6 +16725,12 @@
       <c r="N190" t="n">
         <v>2.959058496322896</v>
       </c>
+      <c r="O190" t="n">
+        <v>-64.43899099235804</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11561,6 +16779,12 @@
       <c r="N191" t="n">
         <v>2.839990354818593</v>
       </c>
+      <c r="O191" t="n">
+        <v>-30.94306818789769</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11609,6 +16833,12 @@
       <c r="N192" t="n">
         <v>2.845809255855761</v>
       </c>
+      <c r="O192" t="n">
+        <v>7.482745003049515</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11657,6 +16887,12 @@
       <c r="N193" t="n">
         <v>4.4541073793489</v>
       </c>
+      <c r="O193" t="n">
+        <v>-44.91163007580862</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11705,6 +16941,12 @@
       <c r="N194" t="n">
         <v>2.692552907771695</v>
       </c>
+      <c r="O194" t="n">
+        <v>24.8882430119429</v>
+      </c>
+      <c r="P194" t="n">
+        <v>22.39941871074862</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11753,6 +16995,12 @@
       <c r="N195" t="n">
         <v>1.360239575980737</v>
       </c>
+      <c r="O195" t="n">
+        <v>-103.3742880560624</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11801,6 +17049,12 @@
       <c r="N196" t="n">
         <v>3.749609027814612</v>
       </c>
+      <c r="O196" t="n">
+        <v>-22.86390975649363</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11849,6 +17103,12 @@
       <c r="N197" t="n">
         <v>1.784467566411076</v>
       </c>
+      <c r="O197" t="n">
+        <v>27.58175617277375</v>
+      </c>
+      <c r="P197" t="n">
+        <v>24.82358055549638</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11897,6 +17157,12 @@
       <c r="N198" t="n">
         <v>2.219983169116753</v>
       </c>
+      <c r="O198" t="n">
+        <v>26.35468395356608</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11945,6 +17211,12 @@
       <c r="N199" t="n">
         <v>3.956750400728553</v>
       </c>
+      <c r="O199" t="n">
+        <v>47.86625422385365</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11993,6 +17265,12 @@
       <c r="N200" t="n">
         <v>4.163835933347038</v>
       </c>
+      <c r="O200" t="n">
+        <v>82.62030960823883</v>
+      </c>
+      <c r="P200" t="n">
+        <v>74.35827864741495</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12041,6 +17319,12 @@
       <c r="N201" t="n">
         <v>6.112534041665102</v>
       </c>
+      <c r="O201" t="n">
+        <v>463.1929420190709</v>
+      </c>
+      <c r="P201" t="n">
+        <v>416.8736478171638</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12089,6 +17373,12 @@
       <c r="N202" t="n">
         <v>5.350024154898936</v>
       </c>
+      <c r="O202" t="n">
+        <v>-73.03572524709408</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12137,6 +17427,12 @@
       <c r="N203" t="n">
         <v>2.001673216504483</v>
       </c>
+      <c r="O203" t="n">
+        <v>49.06421967439406</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12185,6 +17481,12 @@
       <c r="N204" t="n">
         <v>3.705246829791069</v>
       </c>
+      <c r="O204" t="n">
+        <v>122.288722847309</v>
+      </c>
+      <c r="P204" t="n">
+        <v>110.0598505625781</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12233,6 +17535,12 @@
       <c r="N205" t="n">
         <v>3.419054161919797</v>
       </c>
+      <c r="O205" t="n">
+        <v>-16.12168955978296</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12281,6 +17589,12 @@
       <c r="N206" t="n">
         <v>4.078100171648453</v>
       </c>
+      <c r="O206" t="n">
+        <v>-85.40939763311607</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12329,6 +17643,12 @@
       <c r="N207" t="n">
         <v>2.624013652393853</v>
       </c>
+      <c r="O207" t="n">
+        <v>-104.5427234983582</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12377,6 +17697,12 @@
       <c r="N208" t="n">
         <v>4.710139691819289</v>
       </c>
+      <c r="O208" t="n">
+        <v>56.70286729572182</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12425,6 +17751,12 @@
       <c r="N209" t="n">
         <v>2.760546264846576</v>
       </c>
+      <c r="O209" t="n">
+        <v>74.88706100397653</v>
+      </c>
+      <c r="P209" t="n">
+        <v>67.39835490357888</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12473,6 +17805,12 @@
       <c r="N210" t="n">
         <v>2.479257010377573</v>
       </c>
+      <c r="O210" t="n">
+        <v>-50.38711317346859</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12521,6 +17859,12 @@
       <c r="N211" t="n">
         <v>4.496842606486197</v>
       </c>
+      <c r="O211" t="n">
+        <v>39.03897594003591</v>
+      </c>
+      <c r="P211" t="n">
+        <v>35.13507834603232</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12569,6 +17913,12 @@
       <c r="N212" t="n">
         <v>4.610160429791037</v>
       </c>
+      <c r="O212" t="n">
+        <v>-33.55364616877305</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12617,6 +17967,12 @@
       <c r="N213" t="n">
         <v>3.917579364670477</v>
       </c>
+      <c r="O213" t="n">
+        <v>11.23873269539906</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12665,6 +18021,12 @@
       <c r="N214" t="n">
         <v>2.822173113901281</v>
       </c>
+      <c r="O214" t="n">
+        <v>236.5328548522812</v>
+      </c>
+      <c r="P214" t="n">
+        <v>212.8795693670531</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12713,6 +18075,12 @@
       <c r="N215" t="n">
         <v>3.4116841390156</v>
       </c>
+      <c r="O215" t="n">
+        <v>-40.14778643795217</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12761,6 +18129,12 @@
       <c r="N216" t="n">
         <v>10.36717546336652</v>
       </c>
+      <c r="O216" t="n">
+        <v>-125.7660346618505</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12809,6 +18183,12 @@
       <c r="N217" t="n">
         <v>2.242263135425679</v>
       </c>
+      <c r="O217" t="n">
+        <v>-74.01839349101176</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12857,6 +18237,12 @@
       <c r="N218" t="n">
         <v>4.054990443994575</v>
       </c>
+      <c r="O218" t="n">
+        <v>-28.92451648813191</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12905,6 +18291,12 @@
       <c r="N219" t="n">
         <v>5.805578672194546</v>
       </c>
+      <c r="O219" t="n">
+        <v>16.41489962370345</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12953,6 +18345,12 @@
       <c r="N220" t="n">
         <v>2.551607272533356</v>
       </c>
+      <c r="O220" t="n">
+        <v>173.4816399859224</v>
+      </c>
+      <c r="P220" t="n">
+        <v>156.1334759873302</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13001,6 +18399,12 @@
       <c r="N221" t="n">
         <v>4.661667945371674</v>
       </c>
+      <c r="O221" t="n">
+        <v>-24.954551442932</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13049,6 +18453,12 @@
       <c r="N222" t="n">
         <v>3.846513994818455</v>
       </c>
+      <c r="O222" t="n">
+        <v>-65.57077408321609</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13097,6 +18507,12 @@
       <c r="N223" t="n">
         <v>2.671550990746136</v>
       </c>
+      <c r="O223" t="n">
+        <v>91.25572906180588</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13145,6 +18561,12 @@
       <c r="N224" t="n">
         <v>4.017209680940195</v>
       </c>
+      <c r="O224" t="n">
+        <v>80.74677829838075</v>
+      </c>
+      <c r="P224" t="n">
+        <v>72.67210046854268</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13193,6 +18615,12 @@
       <c r="N225" t="n">
         <v>3.565425566095667</v>
       </c>
+      <c r="O225" t="n">
+        <v>17.48330033600521</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13241,6 +18669,12 @@
       <c r="N226" t="n">
         <v>3.282052254622096</v>
       </c>
+      <c r="O226" t="n">
+        <v>-96.5363368420609</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13289,6 +18723,12 @@
       <c r="N227" t="n">
         <v>3.727581928742667</v>
       </c>
+      <c r="O227" t="n">
+        <v>-55.45930667911837</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13337,6 +18777,12 @@
       <c r="N228" t="n">
         <v>3.969816246099253</v>
       </c>
+      <c r="O228" t="n">
+        <v>-1.157140462500141</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13385,6 +18831,12 @@
       <c r="N229" t="n">
         <v>4.641688364733706</v>
       </c>
+      <c r="O229" t="n">
+        <v>101.772633241131</v>
+      </c>
+      <c r="P229" t="n">
+        <v>91.5953699170179</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13433,6 +18885,12 @@
       <c r="N230" t="n">
         <v>3.07565963279527</v>
       </c>
+      <c r="O230" t="n">
+        <v>55.35420429087777</v>
+      </c>
+      <c r="P230" t="n">
+        <v>49.81878386179</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13481,6 +18939,12 @@
       <c r="N231" t="n">
         <v>1.366731537380099</v>
       </c>
+      <c r="O231" t="n">
+        <v>-36.01907422318095</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13529,6 +18993,12 @@
       <c r="N232" t="n">
         <v>2.890614905462233</v>
       </c>
+      <c r="O232" t="n">
+        <v>17.16225909279695</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13577,6 +19047,12 @@
       <c r="N233" t="n">
         <v>3.064316393378538</v>
       </c>
+      <c r="O233" t="n">
+        <v>8.512176774206569</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13625,6 +19101,12 @@
       <c r="N234" t="n">
         <v>2.941337092572616</v>
       </c>
+      <c r="O234" t="n">
+        <v>41.49089153537104</v>
+      </c>
+      <c r="P234" t="n">
+        <v>37.34180238183394</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13673,6 +19155,12 @@
       <c r="N235" t="n">
         <v>3.441137587259499</v>
       </c>
+      <c r="O235" t="n">
+        <v>-44.83492154659127</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13721,6 +19209,12 @@
       <c r="N236" t="n">
         <v>5.417399095164117</v>
       </c>
+      <c r="O236" t="n">
+        <v>8.155548224619247</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13769,6 +19263,12 @@
       <c r="N237" t="n">
         <v>3.319302604308125</v>
       </c>
+      <c r="O237" t="n">
+        <v>-4.628066099470573</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13817,6 +19317,12 @@
       <c r="N238" t="n">
         <v>2.137174301240965</v>
       </c>
+      <c r="O238" t="n">
+        <v>-51.68961111571832</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13865,6 +19371,12 @@
       <c r="N239" t="n">
         <v>2.452204104726802</v>
       </c>
+      <c r="O239" t="n">
+        <v>-52.94088584512276</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13913,6 +19425,12 @@
       <c r="N240" t="n">
         <v>3.286663014088828</v>
       </c>
+      <c r="O240" t="n">
+        <v>-39.30989070434458</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13961,6 +19479,12 @@
       <c r="N241" t="n">
         <v>5.969283553441974</v>
       </c>
+      <c r="O241" t="n">
+        <v>86.53854433989741</v>
+      </c>
+      <c r="P241" t="n">
+        <v>77.88468990590768</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14009,6 +19533,12 @@
       <c r="N242" t="n">
         <v>2.362978663731749</v>
       </c>
+      <c r="O242" t="n">
+        <v>241.5444110325868</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14057,6 +19587,12 @@
       <c r="N243" t="n">
         <v>2.457085446028822</v>
       </c>
+      <c r="O243" t="n">
+        <v>-129.8915719583773</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14105,6 +19641,12 @@
       <c r="N244" t="n">
         <v>2.400467937147388</v>
       </c>
+      <c r="O244" t="n">
+        <v>16.23056390233085</v>
+      </c>
+      <c r="P244" t="n">
+        <v>14.60750751209777</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14153,6 +19695,12 @@
       <c r="N245" t="n">
         <v>4.059165193775828</v>
       </c>
+      <c r="O245" t="n">
+        <v>-16.85521042800167</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14201,6 +19749,12 @@
       <c r="N246" t="n">
         <v>2.842473269774081</v>
       </c>
+      <c r="O246" t="n">
+        <v>-28.18502235400136</v>
+      </c>
+      <c r="P246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14249,6 +19803,12 @@
       <c r="N247" t="n">
         <v>3.071616397552432</v>
       </c>
+      <c r="O247" t="n">
+        <v>69.19099713510055</v>
+      </c>
+      <c r="P247" t="n">
+        <v>62.2718974215905</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14297,6 +19857,12 @@
       <c r="N248" t="n">
         <v>2.026913156072324</v>
       </c>
+      <c r="O248" t="n">
+        <v>380.1477057122352</v>
+      </c>
+      <c r="P248" t="n">
+        <v>342.1329351410117</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14345,6 +19911,12 @@
       <c r="N249" t="n">
         <v>2.663168674020417</v>
       </c>
+      <c r="O249" t="n">
+        <v>85.72762352689665</v>
+      </c>
+      <c r="P249" t="n">
+        <v>77.15486117420699</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14393,6 +19965,12 @@
       <c r="N250" t="n">
         <v>3.377643265427233</v>
       </c>
+      <c r="O250" t="n">
+        <v>-60.79385643414879</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14441,6 +20019,12 @@
       <c r="N251" t="n">
         <v>3.280119443746859</v>
       </c>
+      <c r="O251" t="n">
+        <v>10.73355680167914</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14489,6 +20073,12 @@
       <c r="N252" t="n">
         <v>2.920528706269209</v>
       </c>
+      <c r="O252" t="n">
+        <v>-92.61640282658989</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14537,6 +20127,12 @@
       <c r="N253" t="n">
         <v>4.10027219803885</v>
       </c>
+      <c r="O253" t="n">
+        <v>5.595211429380816</v>
+      </c>
+      <c r="P253" t="n">
+        <v>5.035690286442735</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14585,6 +20181,12 @@
       <c r="N254" t="n">
         <v>3.932554324955636</v>
       </c>
+      <c r="O254" t="n">
+        <v>69.57081849775366</v>
+      </c>
+      <c r="P254" t="n">
+        <v>62.6137366479783</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14633,6 +20235,12 @@
       <c r="N255" t="n">
         <v>4.700474654366952</v>
       </c>
+      <c r="O255" t="n">
+        <v>-127.1677411194858</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14681,6 +20289,12 @@
       <c r="N256" t="n">
         <v>4.114096110060477</v>
       </c>
+      <c r="O256" t="n">
+        <v>186.8094226820835</v>
+      </c>
+      <c r="P256" t="n">
+        <v>168.1284804138751</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14729,6 +20343,12 @@
       <c r="N257" t="n">
         <v>4.848057427486958</v>
       </c>
+      <c r="O257" t="n">
+        <v>26.34287930039908</v>
+      </c>
+      <c r="P257" t="n">
+        <v>23.70859137035918</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14777,6 +20397,12 @@
       <c r="N258" t="n">
         <v>2.942856311923834</v>
       </c>
+      <c r="O258" t="n">
+        <v>-54.15118708360041</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14825,6 +20451,12 @@
       <c r="N259" t="n">
         <v>6.302805170717349</v>
       </c>
+      <c r="O259" t="n">
+        <v>46.57489402697226</v>
+      </c>
+      <c r="P259" t="n">
+        <v>41.91740462427504</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14873,6 +20505,12 @@
       <c r="N260" t="n">
         <v>3.479305328704466</v>
       </c>
+      <c r="O260" t="n">
+        <v>-50.96498629764812</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14921,6 +20559,12 @@
       <c r="N261" t="n">
         <v>4.353836130942232</v>
       </c>
+      <c r="O261" t="n">
+        <v>-47.5415223499109</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14969,6 +20613,12 @@
       <c r="N262" t="n">
         <v>2.871356467117571</v>
       </c>
+      <c r="O262" t="n">
+        <v>53.1378712792823</v>
+      </c>
+      <c r="P262" t="n">
+        <v>47.82408415135407</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15017,6 +20667,12 @@
       <c r="N263" t="n">
         <v>3.264946148966388</v>
       </c>
+      <c r="O263" t="n">
+        <v>-73.57281053976817</v>
+      </c>
+      <c r="P263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15065,6 +20721,12 @@
       <c r="N264" t="n">
         <v>2.903559869070726</v>
       </c>
+      <c r="O264" t="n">
+        <v>-68.48389945645729</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15113,6 +20775,12 @@
       <c r="N265" t="n">
         <v>4.421931194865573</v>
       </c>
+      <c r="O265" t="n">
+        <v>38.82252205965889</v>
+      </c>
+      <c r="P265" t="n">
+        <v>34.940269853693</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15161,6 +20829,12 @@
       <c r="N266" t="n">
         <v>3.811876296999968</v>
       </c>
+      <c r="O266" t="n">
+        <v>-95.14100450629269</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15209,6 +20883,12 @@
       <c r="N267" t="n">
         <v>2.298739981247412</v>
       </c>
+      <c r="O267" t="n">
+        <v>196.4720992392014</v>
+      </c>
+      <c r="P267" t="n">
+        <v>176.8248893152813</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15257,6 +20937,12 @@
       <c r="N268" t="n">
         <v>4.802856544956764</v>
       </c>
+      <c r="O268" t="n">
+        <v>-24.56255051505488</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15305,6 +20991,12 @@
       <c r="N269" t="n">
         <v>2.313882812779074</v>
       </c>
+      <c r="O269" t="n">
+        <v>-1.571440639912645</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15353,6 +21045,12 @@
       <c r="N270" t="n">
         <v>4.543164910359648</v>
       </c>
+      <c r="O270" t="n">
+        <v>-14.99341461605081</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15401,6 +21099,12 @@
       <c r="N271" t="n">
         <v>5.995335342192865</v>
       </c>
+      <c r="O271" t="n">
+        <v>19.36082988963096</v>
+      </c>
+      <c r="P271" t="n">
+        <v>17.42474690066786</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15449,6 +21153,12 @@
       <c r="N272" t="n">
         <v>2.220935709250369</v>
       </c>
+      <c r="O272" t="n">
+        <v>-107.9339660706136</v>
+      </c>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15497,6 +21207,12 @@
       <c r="N273" t="n">
         <v>5.51840730238779</v>
       </c>
+      <c r="O273" t="n">
+        <v>-55.32600812415995</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15545,6 +21261,12 @@
       <c r="N274" t="n">
         <v>2.723555287872307</v>
       </c>
+      <c r="O274" t="n">
+        <v>-84.39966568878377</v>
+      </c>
+      <c r="P274" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15593,6 +21315,12 @@
       <c r="N275" t="n">
         <v>3.562713339425761</v>
       </c>
+      <c r="O275" t="n">
+        <v>17.97490657251664</v>
+      </c>
+      <c r="P275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15641,6 +21369,12 @@
       <c r="N276" t="n">
         <v>9.356887846163497</v>
       </c>
+      <c r="O276" t="n">
+        <v>-44.07260086746476</v>
+      </c>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15689,6 +21423,12 @@
       <c r="N277" t="n">
         <v>6.669827959558665</v>
       </c>
+      <c r="O277" t="n">
+        <v>-121.9993063268497</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15737,6 +21477,12 @@
       <c r="N278" t="n">
         <v>2.589166469088957</v>
       </c>
+      <c r="O278" t="n">
+        <v>5.963024153374717</v>
+      </c>
+      <c r="P278" t="n">
+        <v>5.366721738037246</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15785,6 +21531,12 @@
       <c r="N279" t="n">
         <v>2.760525592430823</v>
       </c>
+      <c r="O279" t="n">
+        <v>23.78659198152427</v>
+      </c>
+      <c r="P279" t="n">
+        <v>21.40793278337184</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15833,6 +21585,12 @@
       <c r="N280" t="n">
         <v>12.26639439619468</v>
       </c>
+      <c r="O280" t="n">
+        <v>-13.61865673700452</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15881,6 +21639,12 @@
       <c r="N281" t="n">
         <v>3.960062215352657</v>
       </c>
+      <c r="O281" t="n">
+        <v>-31.65908110018965</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15929,6 +21693,12 @@
       <c r="N282" t="n">
         <v>2.627670980072193</v>
       </c>
+      <c r="O282" t="n">
+        <v>-24.028260642932</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15977,6 +21747,12 @@
       <c r="N283" t="n">
         <v>3.554466944940253</v>
       </c>
+      <c r="O283" t="n">
+        <v>24.43705486734269</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16025,6 +21801,12 @@
       <c r="N284" t="n">
         <v>2.098275241971734</v>
       </c>
+      <c r="O284" t="n">
+        <v>60.21741919529228</v>
+      </c>
+      <c r="P284" t="n">
+        <v>54.19567727576305</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16073,6 +21855,12 @@
       <c r="N285" t="n">
         <v>3.473325972851471</v>
       </c>
+      <c r="O285" t="n">
+        <v>-195.6892772045491</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16121,6 +21909,12 @@
       <c r="N286" t="n">
         <v>2.426688728036349</v>
       </c>
+      <c r="O286" t="n">
+        <v>-1.283464234276826</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16169,6 +21963,12 @@
       <c r="N287" t="n">
         <v>1.993757447415338</v>
       </c>
+      <c r="O287" t="n">
+        <v>75.82536598911213</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16217,6 +22017,12 @@
       <c r="N288" t="n">
         <v>3.838574826415329</v>
       </c>
+      <c r="O288" t="n">
+        <v>-29.00962554647958</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16265,6 +22071,12 @@
       <c r="N289" t="n">
         <v>3.653298930064595</v>
       </c>
+      <c r="O289" t="n">
+        <v>-126.539279788302</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16313,6 +22125,12 @@
       <c r="N290" t="n">
         <v>5.372340864095855</v>
       </c>
+      <c r="O290" t="n">
+        <v>-419.9597793054909</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16361,6 +22179,12 @@
       <c r="N291" t="n">
         <v>3.130459648608461</v>
       </c>
+      <c r="O291" t="n">
+        <v>75.2499043968232</v>
+      </c>
+      <c r="P291" t="n">
+        <v>67.72491395714088</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16409,6 +22233,12 @@
       <c r="N292" t="n">
         <v>4.688230690464892</v>
       </c>
+      <c r="O292" t="n">
+        <v>7.281130432353793</v>
+      </c>
+      <c r="P292" t="n">
+        <v>6.553017389118414</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16457,6 +22287,12 @@
       <c r="N293" t="n">
         <v>2.322946682116185</v>
       </c>
+      <c r="O293" t="n">
+        <v>58.54089509981387</v>
+      </c>
+      <c r="P293" t="n">
+        <v>52.68680558983249</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16505,6 +22341,12 @@
       <c r="N294" t="n">
         <v>4.830791099395697</v>
       </c>
+      <c r="O294" t="n">
+        <v>40.44964359423731</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16553,6 +22395,12 @@
       <c r="N295" t="n">
         <v>4.055398701429202</v>
       </c>
+      <c r="O295" t="n">
+        <v>-184.4013320635036</v>
+      </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16601,6 +22449,12 @@
       <c r="N296" t="n">
         <v>2.56961816850543</v>
       </c>
+      <c r="O296" t="n">
+        <v>281.8206508944552</v>
+      </c>
+      <c r="P296" t="n">
+        <v>253.6385858050097</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16649,6 +22503,12 @@
       <c r="N297" t="n">
         <v>3.52755014438742</v>
       </c>
+      <c r="O297" t="n">
+        <v>-286.2811014431198</v>
+      </c>
+      <c r="P297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -16697,6 +22557,12 @@
       <c r="N298" t="n">
         <v>3.464103997802346</v>
       </c>
+      <c r="O298" t="n">
+        <v>110.4170301016758</v>
+      </c>
+      <c r="P298" t="n">
+        <v>99.37532709150824</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16745,6 +22611,12 @@
       <c r="N299" t="n">
         <v>4.260242320295513</v>
       </c>
+      <c r="O299" t="n">
+        <v>-14.73363178215924</v>
+      </c>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16793,6 +22665,12 @@
       <c r="N300" t="n">
         <v>2.214365561005602</v>
       </c>
+      <c r="O300" t="n">
+        <v>21.08602263704966</v>
+      </c>
+      <c r="P300" t="n">
+        <v>18.97742037334469</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16840,6 +22718,12 @@
       </c>
       <c r="N301" t="n">
         <v>3.072410619188877</v>
+      </c>
+      <c r="O301" t="n">
+        <v>38.34968676407816</v>
+      </c>
+      <c r="P301" t="n">
+        <v>34.51471808767035</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/e2e/E2E_Results.xlsx
+++ b/output/reports/e2e/E2E_Results.xlsx
@@ -20,8 +20,10 @@
     <sheet name="Jurisdictions_2027" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Jurisdictions_2030" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Jurisdiction_Credit" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Output_Floor_WhatIf" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="FR_Y9C" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Jurisdiction_Securitisation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Jurisdiction_FRTB" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Output_Floor_WhatIf" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="FR_Y9C" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +471,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -490,7 +492,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -511,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -532,7 +534,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.122</v>
+        <v>0.17</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -553,7 +555,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -578,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15 tranches  exposure $48,500M  RWA $64,780M</t>
+          <t>15 tranches  exposure $48,500M  RWA $51,346M</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -616,11 +618,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.598</v>
+        <v>0.606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>167 sensitivities  SBM $16,260M  DRC $136M  RRAO $80M  RWA $205,949M</t>
+          <t>167 sensitivities  SBM $16,142M  DRC $136M  RRAO $80M  RWA $204,466M</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -637,7 +639,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -662,7 +664,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>total RWA $1,701,564M  (credit 70%, market 12%, op 10%, CVA 7%)</t>
+          <t>total RWA $1,686,647M  (credit 70%, market 12%, op 11%, CVA 7%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -700,7 +702,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -725,7 +727,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>severely adverse min CET1 6.71% (Q9), SCB 5.51%, pass=True</t>
+          <t>severely adverse min CET1 6.77% (Q9), SCB 5.56%, pass=True</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -746,7 +748,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CET1 12.22%  T1 13.63%  Total 16.37%  SLR 5.91%  PCA WELL_CAPITALIZED</t>
+          <t>CET1 12.33%  T1 13.76%  Total 16.52%  SLR 5.91%  PCA WELL_CAPITALIZED</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -763,7 +765,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -826,11 +828,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.26</v>
+        <v>0.466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BCBS CET1 11.5% | US CET1 13.1% | UK CET1 12.7% | EU CET1 12.2% | SG CET1 11.6% | CA CET1 11.7%</t>
+          <t>BCBS CET1 11.7% | US CET1 13.2% | UK CET1 12.8% | EU CET1 12.1% | SG CET1 11.7% | CA CET1 11.8%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -968,7 +970,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64780.46070556622</v>
+        <v>51345.83745452524</v>
       </c>
     </row>
     <row r="13">
@@ -1028,7 +1030,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1191868.011104866</v>
+        <v>1178433.387853825</v>
       </c>
     </row>
     <row r="19">
@@ -1038,7 +1040,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>205948.6017911971</v>
+        <v>204466.0667840441</v>
       </c>
     </row>
     <row r="20">
@@ -1068,7 +1070,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1701563.681729855</v>
+        <v>1686646.523471661</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,70 +1155,120 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>market_sbm</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>market_drc</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>market_rrao</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>market_binding_scenario</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>securitisation_exposure</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>securitisation_rwa</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ccp_rwa</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>standardised_rwa</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>modelled_rwa</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>floor_applies</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>floor_factor</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>floor_add_on</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>total_rwa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>cet1_ratio</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>tier1_ratio</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>total_capital_ratio</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>leverage_exposure</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>leverage_exclusions</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>leverage_ratio</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>large_exposures_reportable</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>large_exposure_max_pct_tier1</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>cet1_requirement</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>cet1_surplus</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>leverage_requirement</t>
         </is>
@@ -1266,46 +1318,78 @@
         <v>332124.599064379</v>
       </c>
       <c r="M2" t="n">
-        <v>205948.6017911971</v>
+        <v>206232.795394049</v>
       </c>
       <c r="N2" t="n">
-        <v>64780.46070556622</v>
+        <v>16414.44813474237</v>
       </c>
       <c r="O2" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="b">
-        <v>1</v>
+        <v>4.175496781551914</v>
+      </c>
+      <c r="P2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R2" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S2" t="n">
+        <v>35554</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7377.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.7</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1152901737067579</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.1285928860575376</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.154435874673844</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.116684898052519</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1301485401355019</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.1563041646359564</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3753092.761918609</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.06181568501424406</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.09</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0.02529017370675789</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AJ2" t="n">
+        <v>0.026684898052519</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -1353,46 +1437,78 @@
         <v>190350</v>
       </c>
       <c r="M3" t="n">
-        <v>205948.6017911971</v>
+        <v>203177.0616648263</v>
       </c>
       <c r="N3" t="n">
-        <v>64780.46070556622</v>
+        <v>16141.58616975735</v>
       </c>
       <c r="O3" t="n">
-        <v>1587089.157222958</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="b">
-        <v>0</v>
+        <v>32.5787634287525</v>
+      </c>
+      <c r="P3" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>48500</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>51345.83745452524</v>
       </c>
       <c r="T3" t="n">
-        <v>1587089.157222958</v>
+        <v>7377.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1310575395549625</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.1461795633497659</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1755569022322165</v>
+        <v>1578260.493845546</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="b">
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05912372751928002</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1341448928298715</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.003087353274908972</v>
+        <v>1578260.493845546</v>
       </c>
       <c r="AA3" t="n">
+        <v>0.1317906649828083</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1469972801731323</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.1765389535472139</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3751420.633918609</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.06184323823949877</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1346326091842035</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.002841944201395191</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1440,46 +1556,78 @@
         <v>255795.5202730408</v>
       </c>
       <c r="M4" t="n">
-        <v>205948.6017911971</v>
+        <v>206390.8910314933</v>
       </c>
       <c r="N4" t="n">
-        <v>64780.46070556622</v>
+        <v>16415.1097888347</v>
       </c>
       <c r="O4" t="n">
-        <v>1643859.738104304</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="b">
-        <v>1</v>
+        <v>16.16149368476346</v>
+      </c>
+      <c r="P4" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R4" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S4" t="n">
+        <v>34554</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7377.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1621453.066639035</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
         <v>0.6</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1643859.738104304</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1265314766087435</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1411312623712908</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.1694940569137066</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1621453.066639035</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1282800003771584</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1430815388822151</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1718362755857853</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3433092.761918609</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>320000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.06757755064863004</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>920</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.09</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0.03653147660874351</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AJ4" t="n">
+        <v>0.0382800003771584</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -1527,46 +1675,78 @@
         <v>256347.7874999999</v>
       </c>
       <c r="M5" t="n">
-        <v>205948.6017911971</v>
+        <v>230301.4988588616</v>
       </c>
       <c r="N5" t="n">
-        <v>64780.46070556622</v>
+        <v>18339.94441192738</v>
       </c>
       <c r="O5" t="n">
-        <v>1710595.182876365</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="b">
-        <v>1</v>
+        <v>4.175496781551914</v>
+      </c>
+      <c r="P5" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R5" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S5" t="n">
+        <v>34554</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7377.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1712099.119238463</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="b">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
         <v>0.6</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1710595.182876365</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1215951044888646</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.1356253088529644</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.1628815857764167</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1712099.119238463</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1214882933252824</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1355061733243534</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1627385078805094</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3753092.761918609</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.06181568501424406</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>878</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.09</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0.0315951044888646</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AJ5" t="n">
+        <v>0.0314882933252824</v>
+      </c>
+      <c r="AK5" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -1614,46 +1794,74 @@
         <v>331502.8314298259</v>
       </c>
       <c r="M6" t="n">
-        <v>205948.6017911971</v>
+        <v>204466.0667840441</v>
       </c>
       <c r="N6" t="n">
-        <v>64780.46070556622</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1797707.544028149</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S6" t="n">
+        <v>35554</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7377.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1774376.048315429</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
         <v>0.65</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1797707.544028149</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1157029132413449</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.129053249384577</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.1549887560598895</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1774376.048315429</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1172243055227626</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1307501869292352</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1570267228713577</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3753092.761918609</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.06181568501424406</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0.11</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0.005702913241344851</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="AJ6" t="n">
+        <v>0.00722430552276257</v>
+      </c>
+      <c r="AK6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -1701,47 +1909,79 @@
         <v>332087.9674948845</v>
       </c>
       <c r="M7" t="n">
-        <v>205948.6017911971</v>
+        <v>206232.7953940489</v>
       </c>
       <c r="N7" t="n">
-        <v>64780.46070556622</v>
+        <v>16414.44813474236</v>
       </c>
       <c r="O7" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="b">
-        <v>1</v>
+        <v>4.175496781551914</v>
+      </c>
+      <c r="P7" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R7" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S7" t="n">
+        <v>35554</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7777.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.675</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1169477780071718</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.1304417523926147</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.1566563030223056</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1183562011440252</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1320126858914127</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1585429430719952</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3753092.761918609</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.06181568501424406</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.09</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0.02694777800717177</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.035</v>
+      <c r="AJ7" t="n">
+        <v>0.02835620114402519</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -1755,7 +1995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1826,70 +2066,120 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>market_sbm</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>market_drc</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>market_rrao</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>market_binding_scenario</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>securitisation_exposure</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>securitisation_rwa</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ccp_rwa</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>standardised_rwa</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>modelled_rwa</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>floor_applies</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>floor_factor</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>floor_add_on</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>total_rwa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>cet1_ratio</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>tier1_ratio</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>total_capital_ratio</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>leverage_exposure</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>leverage_exclusions</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>leverage_ratio</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>large_exposures_reportable</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>large_exposure_max_pct_tier1</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>cet1_requirement</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>cet1_surplus</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>leverage_requirement</t>
         </is>
@@ -1939,46 +2229,78 @@
         <v>332124.599064379</v>
       </c>
       <c r="M2" t="n">
-        <v>205948.6017911971</v>
+        <v>206232.795394049</v>
       </c>
       <c r="N2" t="n">
-        <v>64780.46070556622</v>
+        <v>16414.44813474237</v>
       </c>
       <c r="O2" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="b">
-        <v>1</v>
+        <v>4.175496781551914</v>
+      </c>
+      <c r="P2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R2" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S2" t="n">
+        <v>35554</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7377.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.725</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1152901737067579</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.1285928860575376</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.154435874673844</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.116684898052519</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1301485401355019</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.1563041646359564</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3753092.761918609</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.06181568501424406</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.09</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0.02529017370675789</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AJ2" t="n">
+        <v>0.026684898052519</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -2026,46 +2348,78 @@
         <v>190350</v>
       </c>
       <c r="M3" t="n">
-        <v>205948.6017911971</v>
+        <v>203177.0616648263</v>
       </c>
       <c r="N3" t="n">
-        <v>64780.46070556622</v>
+        <v>16141.58616975735</v>
       </c>
       <c r="O3" t="n">
-        <v>1587089.157222958</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="b">
-        <v>0</v>
+        <v>32.5787634287525</v>
+      </c>
+      <c r="P3" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>48500</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>51345.83745452524</v>
       </c>
       <c r="T3" t="n">
-        <v>1587089.157222958</v>
+        <v>7377.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1310575395549625</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.1461795633497659</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1755569022322165</v>
+        <v>1578260.493845546</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="b">
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05912372751928002</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1341448928298715</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.003087353274908972</v>
+        <v>1578260.493845546</v>
       </c>
       <c r="AA3" t="n">
+        <v>0.1317906649828083</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1469972801731323</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.1765389535472139</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3751420.633918609</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.06184323823949877</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1346326091842035</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.002841944201395191</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2113,46 +2467,78 @@
         <v>255795.5202730408</v>
       </c>
       <c r="M4" t="n">
-        <v>205948.6017911971</v>
+        <v>206390.8910314933</v>
       </c>
       <c r="N4" t="n">
-        <v>64780.46070556622</v>
+        <v>16415.1097888347</v>
       </c>
       <c r="O4" t="n">
-        <v>1652580.792833884</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="b">
-        <v>1</v>
+        <v>16.16149368476346</v>
+      </c>
+      <c r="P4" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R4" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S4" t="n">
+        <v>34554</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7377.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1630174.121368614</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
         <v>0.725</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1652580.792833884</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1258637404609531</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1403864797449092</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.1685995971976717</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1630174.121368614</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1275937320274557</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1423160857229314</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1709169912318829</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3433092.761918609</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>320000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.06757755064863004</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>920</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.09</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0.03586374046095309</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AJ4" t="n">
+        <v>0.03759373202745572</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -2200,46 +2586,78 @@
         <v>256347.7874999999</v>
       </c>
       <c r="M5" t="n">
-        <v>205948.6017911971</v>
+        <v>230301.4988588616</v>
       </c>
       <c r="N5" t="n">
-        <v>64780.46070556622</v>
+        <v>18339.94441192738</v>
       </c>
       <c r="O5" t="n">
-        <v>1720836.720924312</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="b">
-        <v>1</v>
+        <v>4.175496781551914</v>
+      </c>
+      <c r="P5" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R5" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S5" t="n">
+        <v>34554</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7377.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1722340.65728641</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="b">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
         <v>0.725</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1720836.720924312</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1208714327575931</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.1348181365373154</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.1619121980723101</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1722340.65728641</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.120765888629552</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1347004142406542</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.16177081742202</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3753092.761918609</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.06181568501424406</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>878</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.09</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0.03087143275759315</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AJ5" t="n">
+        <v>0.03076588862955201</v>
+      </c>
+      <c r="AK5" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -2287,46 +2705,74 @@
         <v>331502.8314298259</v>
       </c>
       <c r="M6" t="n">
-        <v>205948.6017911971</v>
+        <v>204466.0667840441</v>
       </c>
       <c r="N6" t="n">
-        <v>64780.46070556622</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1803521.580514534</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S6" t="n">
+        <v>35554</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7377.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1780190.084801815</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
         <v>0.725</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1803521.580514534</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1153299202223346</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.128637218709527</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.1544891167473093</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1780190.084801815</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1168414551770499</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1303231615436326</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1565138792689211</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3753092.761918609</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.06181568501424406</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0.11</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0.005329920222334569</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="AJ6" t="n">
+        <v>0.006841455177049913</v>
+      </c>
+      <c r="AK6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -2374,47 +2820,79 @@
         <v>332087.9674948845</v>
       </c>
       <c r="M7" t="n">
-        <v>205948.6017911971</v>
+        <v>206232.7953940489</v>
       </c>
       <c r="N7" t="n">
-        <v>64780.46070556622</v>
+        <v>16414.44813474236</v>
       </c>
       <c r="O7" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="b">
-        <v>1</v>
+        <v>4.175496781551914</v>
+      </c>
+      <c r="P7" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
       <c r="R7" t="n">
+        <v>48500</v>
+      </c>
+      <c r="S7" t="n">
+        <v>35554</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7777.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.675</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1169477780071718</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.1304417523926147</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.1566563030223056</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.05912372751928002</v>
-      </c>
       <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1183562011440252</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1320126858914127</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1585429430719952</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3753092.761918609</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.06181568501424406</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1235202448275051</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.09</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0.02694777800717177</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.035</v>
+      <c r="AJ7" t="n">
+        <v>0.02835620114402519</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -3629,7 +4107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3640,45 +4118,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>tranche</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>modelled_to_sa</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>floor_factor</t>
+          <t>risk_weight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>floor_applies</t>
+          <t>rwa</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>standardised_rwa</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>modelled_rwa</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>floored_rwa</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>add_on</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
@@ -3687,1296 +4145,2520 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jurisdiction.BCBS</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.5</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="G2" t="n">
-        <v>902071.6740745436</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1262900.343704361</v>
-      </c>
-      <c r="I2" t="n">
-        <v>360828.6696298174</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        <v>0.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jurisdiction.BCBS</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.6</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1082486.008889452</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1262900.343704361</v>
-      </c>
-      <c r="I3" t="n">
-        <v>180414.3348149085</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        <v>1.584</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jurisdiction.BCBS</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1262900.343704361</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1262900.343704361</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        <v>7.22</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5415</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jurisdiction.US</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.5</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RMBS-2-SNR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1587089.157222958</v>
-      </c>
-      <c r="G5" t="n">
-        <v>793544.578611479</v>
-      </c>
-      <c r="H5" t="n">
-        <v>793544.578611479</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        <v>0.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jurisdiction.US</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RMBS-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1587089.157222958</v>
-      </c>
-      <c r="G6" t="n">
-        <v>952253.4943337748</v>
-      </c>
-      <c r="H6" t="n">
-        <v>952253.4943337748</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        <v>1.584</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jurisdiction.US</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.7</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RMBS-2-JNR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1587089.157222958</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1110962.410056071</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1110962.410056071</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        <v>7.22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jurisdiction.UK</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.5</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1643859.738104304</v>
-      </c>
-      <c r="G8" t="n">
-        <v>821929.8690521521</v>
-      </c>
-      <c r="H8" t="n">
-        <v>986315.8428625824</v>
-      </c>
-      <c r="I8" t="n">
-        <v>164385.9738104304</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        <v>0.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jurisdiction.UK</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.6</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1643859.738104304</v>
-      </c>
-      <c r="G9" t="n">
-        <v>986315.8428625825</v>
-      </c>
-      <c r="H9" t="n">
-        <v>986315.8428625826</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        <v>1.584</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1520.64</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jurisdiction.UK</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1643859.738104304</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1150701.816673013</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1150701.816673013</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        <v>7.22</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2888</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jurisdiction.EU</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.5</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CLO-1-SNR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1710595.182876365</v>
-      </c>
-      <c r="G11" t="n">
-        <v>855297.5914381823</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1026357.109725819</v>
-      </c>
-      <c r="I11" t="n">
-        <v>171059.5182876365</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        <v>0.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jurisdiction.EU</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.6</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CLO-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1710595.182876365</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1026357.109725819</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1026357.109725819</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        <v>1.584</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jurisdiction.EU</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.7</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CLO-1-JNR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1710595.182876365</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1197416.628013455</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1197416.628013455</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        <v>7.22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jurisdiction.SG</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.5</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CLO-2-SNR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1797707.544028149</v>
-      </c>
-      <c r="G14" t="n">
-        <v>898853.7720140743</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1168509.903618297</v>
-      </c>
-      <c r="I14" t="n">
-        <v>269656.1316042223</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        <v>0.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jurisdiction.SG</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.6</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CLO-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1797707.544028149</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1078624.526416889</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1168509.903618297</v>
-      </c>
-      <c r="I15" t="n">
-        <v>89885.37720140751</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        <v>1.584</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1330.56</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jurisdiction.SG</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.7</v>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CLO-2-JNR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1797707.544028149</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1258395.280819704</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1258395.280819704</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        <v>7.22</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2527</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CRE42.4 Table 2, CRE42.5-42.7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jurisdiction.CA</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.5</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="G17" t="n">
-        <v>889285.8143369107</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1200535.849354829</v>
-      </c>
-      <c r="I17" t="n">
-        <v>311250.0350179188</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        <v>0.15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jurisdiction.CA</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1067142.977204293</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1200535.849354829</v>
-      </c>
-      <c r="I18" t="n">
-        <v>133392.8721505366</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        <v>0.4583549571052741</v>
+      </c>
+      <c r="E18" t="n">
+        <v>825.0389227894934</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jurisdiction.CA</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.7</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1245000.140071675</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1245000.140071675</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        <v>8.007544584284378</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6005.658438213284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jurisdiction.BCBS</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.5</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RMBS-2-SNR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="G20" t="n">
-        <v>902071.6740745436</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1308003.927408088</v>
-      </c>
-      <c r="I20" t="n">
-        <v>405932.2533335446</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        <v>0.15</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jurisdiction.BCBS</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RMBS-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1082486.008889452</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1308003.927408088</v>
-      </c>
-      <c r="I21" t="n">
-        <v>225517.9185186358</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        <v>0.4489212217671813</v>
+      </c>
+      <c r="E21" t="n">
+        <v>538.7054661206175</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jurisdiction.BCBS</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.7</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RMBS-2-JNR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1804143.348149087</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1262900.343704361</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1308003.927408088</v>
-      </c>
-      <c r="I22" t="n">
-        <v>45103.58370372729</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        <v>7.955403539169664</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3977.701769584832</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jurisdiction.US</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.5</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1587089.157222958</v>
-      </c>
-      <c r="G23" t="n">
-        <v>793544.578611479</v>
-      </c>
-      <c r="H23" t="n">
-        <v>793544.578611479</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        <v>0.15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>960</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jurisdiction.US</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.6</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1587089.157222958</v>
-      </c>
-      <c r="G24" t="n">
-        <v>952253.4943337748</v>
-      </c>
-      <c r="H24" t="n">
-        <v>952253.4943337748</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        <v>6.193864072554316</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5946.109509652144</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jurisdiction.US</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.7</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RW_1250</t>
+        </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1587089.157222958</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1110962.410056071</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1110962.410056071</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        <v>12.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jurisdiction.UK</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.5</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CLO-1-SNR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D26" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1643859.738104304</v>
-      </c>
-      <c r="G26" t="n">
-        <v>821929.8690521521</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1191798.310125621</v>
-      </c>
-      <c r="I26" t="n">
-        <v>369868.4410734685</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        <v>0.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jurisdiction.UK</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.6</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CLO-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D27" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1643859.738104304</v>
-      </c>
-      <c r="G27" t="n">
-        <v>986315.8428625825</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1191798.310125621</v>
-      </c>
-      <c r="I27" t="n">
-        <v>205482.467263038</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        <v>5.661287535149168</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6793.545042179002</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jurisdiction.UK</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.7</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CLO-1-JNR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RW_1250</t>
+        </is>
       </c>
       <c r="D28" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1643859.738104304</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1150701.816673013</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1191798.310125621</v>
-      </c>
-      <c r="I28" t="n">
-        <v>41096.49345260759</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        <v>12.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6250</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jurisdiction.EU</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.5</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CLO-2-SNR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D29" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1710595.182876365</v>
-      </c>
-      <c r="G29" t="n">
-        <v>855297.5914381823</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1240181.507585364</v>
-      </c>
-      <c r="I29" t="n">
-        <v>384883.9161471821</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>CRR Art. 92(3)</t>
+        <v>0.15</v>
+      </c>
+      <c r="E29" t="n">
+        <v>840</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jurisdiction.EU</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.6</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CLO-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1710595.182876365</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1026357.109725819</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1240181.507585364</v>
-      </c>
-      <c r="I30" t="n">
-        <v>213824.3978595457</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>CRR Art. 92(3)</t>
+        <v>6.7072360785546</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5634.078305985865</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jurisdiction.EU</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.7</v>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CLO-2-JNR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>RW_1250</t>
+        </is>
       </c>
       <c r="D31" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1710595.182876365</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1197416.628013455</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1240181.507585364</v>
-      </c>
-      <c r="I31" t="n">
-        <v>42764.87957190944</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>CRR Art. 92(3)</t>
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4375</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ERBA NPR § __.133 (SEC-SA)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jurisdiction.SG</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.5</v>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D32" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1797707.544028149</v>
-      </c>
-      <c r="G32" t="n">
-        <v>898853.7720140743</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1303337.969420408</v>
-      </c>
-      <c r="I32" t="n">
-        <v>404484.1974063334</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        <v>0.15</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(1)(b); PRA Rulebook Securitisation (CRR) Part Art 261(1) (p = 1.0)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jurisdiction.SG</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.6</v>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D33" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1797707.544028149</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1078624.526416889</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1303337.969420408</v>
-      </c>
-      <c r="I33" t="n">
-        <v>224713.4430035185</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        <v>1.584</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jurisdiction.SG</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.7</v>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E34" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1797707.544028149</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1258395.280819704</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1303337.969420408</v>
-      </c>
-      <c r="I34" t="n">
-        <v>44942.68860070384</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        <v>7.22</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5415</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jurisdiction.CA</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.5</v>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RMBS-2-SNR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="G35" t="n">
-        <v>889285.8143369107</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1200535.849354829</v>
-      </c>
-      <c r="I35" t="n">
-        <v>311250.0350179188</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        <v>0.15</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(1)(b); PRA Rulebook Securitisation (CRR) Part Art 261(1) (p = 1.0)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jurisdiction.CA</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.6</v>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RMBS-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D36" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E36" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1067142.977204293</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1200535.849354829</v>
-      </c>
-      <c r="I36" t="n">
-        <v>133392.8721505366</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        <v>1.584</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jurisdiction.CA</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.7</v>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RMBS-2-JNR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
       </c>
       <c r="D37" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E37" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1778571.628673821</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1245000.140071675</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1245000.140071675</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        <v>7.22</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1520.64</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2888</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CLO-1-SNR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CLO-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CLO-1-JNR</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CLO-2-SNR</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CLO-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1330.56</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CLO-2-JNR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2527</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Securitisation (CRR) Part Art 254(2) (SEC-ERBA instead of SEC-SA); PRA Rulebook Securitisation (CRR) Part Art 263(3) Table 2, Art 263(4)-(6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(1)(b), 261</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>RMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5415</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RMBS-2-SNR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SEC_SA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(1)(b), 261</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RMBS-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RMBS-2-JNR</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1520.64</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2888</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CLO-1-SNR</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CLO-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CLO-1-JNR</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CLO-2-SNR</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CLO-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1330.56</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLO-2-JNR</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2527</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CRR Art. 254(2)(b) SEC-SA RW &gt; 25 % or SEC-ERBA RW &gt; 75 %; Art. 263</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5415</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RMBS-2-SNR</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RMBS-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RMBS-2-JNR</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1520.64</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2888</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CLO-1-SNR</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CLO-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CLO-1-JNR</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CLO-2-SNR</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CLO-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1330.56</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CLO-2-JNR</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2527</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MAS Notice 637 Part VII Division 6 Sub-division 5, paras 7.6.49-7.6.52, Table 7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>RMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>RMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E79" t="n">
+        <v>5415</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>RMBS-2-SNR</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RMBS-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RMBS-2-JNR</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CMBS-1-SNR</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CMBS-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1520.64</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CMBS-1-JNR</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2888</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CLO-1-SNR</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CLO-1-MEZ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CLO-1-JNR</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CLO-2-SNR</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CLO-2-MEZ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1330.56</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CLO-2-JNR</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SEC_ERBA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2527</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CAR Ch.6 s.6.6.2.2 Table 2 [CRE 42]</t>
         </is>
       </c>
     </row>
@@ -4991,6 +6673,1774 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>risk_class</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>capital_$M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GIRR</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4427.009268437909</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CSR_NONSEC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>9787.493805553651</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>902.8587176988991</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1059.807575969784</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>237.2787670821237</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GIRR</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4427.670922530242</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CSR_NONSEC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9712.155222229752</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>902.8129539779802</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>856.8377852987155</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>242.1092857206584</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GIRR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4427.670922530241</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CSR_NONSEC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9787.493805553653</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>902.8587176988989</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1059.807575969784</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>237.2787670821237</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GIRR</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6267.737052873898</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CSR_NONSEC</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9787.49380555365</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>902.8587176988991</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1059.807575969784</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>322.0472598311444</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GIRR</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4427.009268437907</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CSR_NONSEC</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9787.49380555365</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>902.8587176988991</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1059.807575969784</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>237.2787670821237</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>modelled_to_sa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>floor_factor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>floor_applies</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>standardised_rwa</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>modelled_rwa</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>floored_rwa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>add_on</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="G2" t="n">
+        <v>891289.2905231866</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1247805.006732461</v>
+      </c>
+      <c r="I2" t="n">
+        <v>356515.7162092746</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1069547.148627824</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1247805.006732461</v>
+      </c>
+      <c r="I3" t="n">
+        <v>178257.8581046372</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1247805.006732461</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1247805.006732461</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1578260.493845546</v>
+      </c>
+      <c r="G5" t="n">
+        <v>789130.2469227732</v>
+      </c>
+      <c r="H5" t="n">
+        <v>789130.2469227732</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1578260.493845546</v>
+      </c>
+      <c r="G6" t="n">
+        <v>946956.2963073278</v>
+      </c>
+      <c r="H6" t="n">
+        <v>946956.2963073278</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1578260.493845546</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1104782.345691882</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1104782.345691882</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1621453.066639035</v>
+      </c>
+      <c r="G8" t="n">
+        <v>810726.5333195173</v>
+      </c>
+      <c r="H8" t="n">
+        <v>972871.8399834207</v>
+      </c>
+      <c r="I8" t="n">
+        <v>162145.3066639034</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1621453.066639035</v>
+      </c>
+      <c r="G9" t="n">
+        <v>972871.8399834207</v>
+      </c>
+      <c r="H9" t="n">
+        <v>972871.8399834207</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1621453.066639035</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1135017.146647324</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1135017.146647324</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}; Art 92(5)(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1712099.119238463</v>
+      </c>
+      <c r="G11" t="n">
+        <v>856049.5596192315</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1027259.471543078</v>
+      </c>
+      <c r="I11" t="n">
+        <v>171209.9119238463</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1712099.119238463</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1027259.471543078</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1027259.471543078</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1712099.119238463</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1198469.383466924</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1198469.383466924</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3); Art. 465(1) x = 60.0%; Art. 465(2) cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1774376.048315429</v>
+      </c>
+      <c r="G14" t="n">
+        <v>887188.0241577147</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1153344.431405029</v>
+      </c>
+      <c r="I14" t="n">
+        <v>266156.4072473145</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1774376.048315429</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1064625.628989258</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1153344.431405029</v>
+      </c>
+      <c r="I15" t="n">
+        <v>88718.80241577154</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1774376.048315429</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1242063.2338208</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1242063.2338208</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="G17" t="n">
+        <v>878703.4307855536</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1186249.631560497</v>
+      </c>
+      <c r="I17" t="n">
+        <v>307546.2007749439</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1054444.116942664</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1186249.631560497</v>
+      </c>
+      <c r="I18" t="n">
+        <v>131805.5146178332</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1230184.803099775</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1230184.803099775</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="G20" t="n">
+        <v>891289.2905231866</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1292369.47125862</v>
+      </c>
+      <c r="I20" t="n">
+        <v>401080.180735434</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1069547.148627824</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1292369.47125862</v>
+      </c>
+      <c r="I21" t="n">
+        <v>222822.3226307966</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jurisdiction.BCBS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1782578.581046373</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1247805.006732461</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1292369.47125862</v>
+      </c>
+      <c r="I22" t="n">
+        <v>44564.46452615938</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>RBC20.4(2) / RBC90.1 Table 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1578260.493845546</v>
+      </c>
+      <c r="G23" t="n">
+        <v>789130.2469227732</v>
+      </c>
+      <c r="H23" t="n">
+        <v>789130.2469227732</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1578260.493845546</v>
+      </c>
+      <c r="G24" t="n">
+        <v>946956.2963073278</v>
+      </c>
+      <c r="H24" t="n">
+        <v>946956.2963073278</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jurisdiction.US</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1578260.493845546</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1104782.345691882</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1104782.345691882</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ERBA NPR (March 2026): no output floor; no internal models for credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1621453.066639035</v>
+      </c>
+      <c r="G26" t="n">
+        <v>810726.5333195173</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1175553.4733133</v>
+      </c>
+      <c r="I26" t="n">
+        <v>364826.9399937828</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1621453.066639035</v>
+      </c>
+      <c r="G27" t="n">
+        <v>972871.8399834207</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1175553.4733133</v>
+      </c>
+      <c r="I27" t="n">
+        <v>202681.6333298793</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Jurisdiction.UK</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1621453.066639035</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1135017.146647324</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1175553.4733133</v>
+      </c>
+      <c r="I28" t="n">
+        <v>40536.32666597593</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PRA Rulebook Required Level of Own Funds (CRR) Part Art 92(2A)(a) TREA = max{U-TREA; x*S-TREA + OF-ADJ}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1712099.119238463</v>
+      </c>
+      <c r="G29" t="n">
+        <v>856049.5596192315</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1241271.861447885</v>
+      </c>
+      <c r="I29" t="n">
+        <v>385222.301828654</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1712099.119238463</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1027259.471543078</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1241271.861447885</v>
+      </c>
+      <c r="I30" t="n">
+        <v>214012.3899048078</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jurisdiction.EU</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1712099.119238463</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1198469.383466924</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1241271.861447885</v>
+      </c>
+      <c r="I31" t="n">
+        <v>42802.47798096138</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>CRR Art. 92(3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1774376.048315429</v>
+      </c>
+      <c r="G32" t="n">
+        <v>887188.0241577147</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1286422.635028686</v>
+      </c>
+      <c r="I32" t="n">
+        <v>399234.6108709715</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1774376.048315429</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1064625.628989258</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1286422.635028686</v>
+      </c>
+      <c r="I33" t="n">
+        <v>221797.0060394286</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Jurisdiction.SG</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1774376.048315429</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1242063.2338208</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1286422.635028686</v>
+      </c>
+      <c r="I34" t="n">
+        <v>44359.40120788569</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>MAS 637 paras 4.1.4, 5.1.1, 5.1.6, Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="G35" t="n">
+        <v>878703.4307855536</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1186249.631560497</v>
+      </c>
+      <c r="I35" t="n">
+        <v>307546.2007749439</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1054444.116942664</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1186249.631560497</v>
+      </c>
+      <c r="I36" t="n">
+        <v>131805.5146178332</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jurisdiction.CA</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1757406.861571107</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1230184.803099775</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1230184.803099775</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CAR Ch.1 s.1.5.1 (paragraph 33: floor adjustment factor 67.5% until further notice) and s.1.5.2 [Basel Framework, RBC 20.11-20.12]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -5074,7 +8524,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'base_report': {'reporting_date': datetime.date(2026, 6, 30), 'total_rwa': 1701563.681729855, 'credit_risk_rwa': 1191868.0111048662, 'market_risk_rwa': 205948.60179119706, 'operational_risk_rwa': 177330.0, 'cva_risk_rwa': 126417.0688337919, 'cet1_ratio': 0.1222405027994848, 'tier1_ratio': 0.13634517619942535, 'total_capital_ratio': 0.16374612305144212, 'leverage_ratio': 0.05912372751928002}, 'ccb_requirement': 0.05514489282987152, 'ccyb_requirement': 0.0, 'gsib_surcharge': 0.034, 'combined_buffer': 0.08914489282987152, 'effective_cet1_minimum': 0.13414489282987152, 'effective_tier1_minimum': 0.14914489282987153, 'effective_total_minimum': 0.16914489282987152, 'cet1_surplus_over_minimum': 131429.63432215655, 'cet1_surplus_over_buffer': -20256.077728853008, 'pca_category': 'WELL_CAPITALIZED', 'is_well_capitalized': True}</t>
+          <t>{'base_report': {'reporting_date': datetime.date(2026, 6, 30), 'total_rwa': 1686646.5234716611, 'credit_risk_rwa': 1178433.3878538252, 'market_risk_rwa': 204466.0667840441, 'operational_risk_rwa': 177330.0, 'cva_risk_rwa': 126417.0688337919, 'cet1_ratio': 0.12332163088438299, 'tier1_ratio': 0.137551049832581, 'total_capital_ratio': 0.16519433807322176, 'leverage_ratio': 0.05912372751928002}, 'ccb_requirement': 0.055632609184203485, 'ccyb_requirement': 0.0, 'gsib_surcharge': 0.034, 'combined_buffer': 0.08963260918420349, 'effective_cet1_minimum': 0.1346326091842035, 'effective_tier1_minimum': 0.14963260918420349, 'effective_total_minimum': 0.1696326091842035, 'cet1_surplus_over_minimum': 132100.90644377525, 'cet1_surplus_over_buffer': -19077.622226455656, 'pca_category': 'WELL_CAPITALIZED', 'is_well_capitalized': True}</t>
         </is>
       </c>
     </row>
@@ -5125,7 +8575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5486,7 +8936,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16,476 in [1,000, 60,000]</t>
+          <t>16,357 in [1,000, 60,000]</t>
         </is>
       </c>
     </row>
@@ -5546,7 +8996,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1,701,564 in [800,000, 2,500,000]</t>
+          <t>1,686,647 in [800,000, 2,500,000]</t>
         </is>
       </c>
     </row>
@@ -5686,7 +9136,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.0671 in [0.0450, 0.2000]</t>
+          <t>0.0677 in [0.0450, 0.2000]</t>
         </is>
       </c>
     </row>
@@ -5706,7 +9156,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.0551 in [0.0250, 0.1000]</t>
+          <t>0.0556 in [0.0250, 0.1000]</t>
         </is>
       </c>
     </row>
@@ -5726,7 +9176,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.1222 in [0.1000, 0.1500]</t>
+          <t>0.1233 in [0.1000, 0.1500]</t>
         </is>
       </c>
     </row>
@@ -5766,7 +9216,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.0551 in [0.0551, 0.0551]</t>
+          <t>0.0556 in [0.0556, 0.0556]</t>
         </is>
       </c>
     </row>
@@ -5967,6 +9417,106 @@
       <c r="D42" t="inlineStr">
         <is>
           <t>1.00 in [1.00, 1.00]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>US adapter FRTB RWA / stage-10 FRTB RWA</t>
+        </is>
+      </c>
+      <c r="C43" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0.994 in [0.950, 1.050]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>US securitisation: SEC-SA / 1,250% only (§ __.133)</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1 in [1, 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>US adapter sec RWA = stage-8 SEC-SA RWA</t>
+        </is>
+      </c>
+      <c r="C45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>51,346 in [51,345, 51,346]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>UK leverage excludes central bank claims (Art 429a(A1)-(A2))</t>
+        </is>
+      </c>
+      <c r="C46" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>320,000 in [320,000, 320,000]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Multi-jurisdiction comparison</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>no large-exposure limit breaches</t>
+        </is>
+      </c>
+      <c r="C47" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0 in [0, 0]</t>
         </is>
       </c>
     </row>
@@ -6003,7 +9553,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1191868.011104866</v>
+        <v>1178433.387853825</v>
       </c>
     </row>
     <row r="3">
@@ -6033,7 +9583,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>205948.6017911971</v>
+        <v>204466.0667840441</v>
       </c>
     </row>
     <row r="6">
@@ -6043,7 +9593,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16475.88814329576</v>
+        <v>16357.28534272353</v>
       </c>
     </row>
     <row r="7">
@@ -6093,7 +9643,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1701563.681729855</v>
+        <v>1686646.523471661</v>
       </c>
     </row>
     <row r="12">
@@ -6103,7 +9653,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1701563.681729855</v>
+        <v>1686646.523471661</v>
       </c>
     </row>
     <row r="13">
@@ -6113,7 +9663,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1233633.669254145</v>
+        <v>1222818.729516954</v>
       </c>
     </row>
     <row r="14">
@@ -6133,7 +9683,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>467930.0124757101</v>
+        <v>463827.7939547068</v>
       </c>
     </row>
   </sheetData>
@@ -6169,7 +9719,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1222405027994848</v>
+        <v>0.123321630884383</v>
       </c>
     </row>
     <row r="3">
@@ -6179,7 +9729,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1363451761994253</v>
+        <v>0.137551049832581</v>
       </c>
     </row>
     <row r="4">
@@ -6189,7 +9739,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1637461230514421</v>
+        <v>0.1651943380732218</v>
       </c>
     </row>
     <row r="5">
@@ -6209,7 +9759,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05514489282987152</v>
+        <v>0.05563260918420349</v>
       </c>
     </row>
     <row r="7">
@@ -6239,7 +9789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05514489282987152</v>
+        <v>0.05563260918420349</v>
       </c>
     </row>
     <row r="10">
@@ -6249,7 +9799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08914489282987152</v>
+        <v>0.08963260918420349</v>
       </c>
     </row>
     <row r="11">
@@ -6259,7 +9809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1341448928298715</v>
+        <v>0.1346326091842035</v>
       </c>
     </row>
     <row r="12">
@@ -6269,7 +9819,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1491448928298715</v>
+        <v>0.1496326091842035</v>
       </c>
     </row>
     <row r="13">
@@ -6279,7 +9829,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1691448928298715</v>
+        <v>0.1696326091842035</v>
       </c>
     </row>
   </sheetData>
@@ -22809,7 +26359,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0543</v>
+        <v>0.04430000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -22828,10 +26378,10 @@
         <v>1800</v>
       </c>
       <c r="E3" t="n">
-        <v>1.084275877467176</v>
+        <v>0.4583549571052738</v>
       </c>
       <c r="F3" t="n">
-        <v>1951.696579440918</v>
+        <v>825.038922789493</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -22839,7 +26389,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.0543</v>
+        <v>0.04430000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -22858,10 +26408,10 @@
         <v>750</v>
       </c>
       <c r="E4" t="n">
-        <v>10.22853666476841</v>
+        <v>8.007544584284378</v>
       </c>
       <c r="F4" t="n">
-        <v>7671.402498576308</v>
+        <v>6005.658438213284</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -22869,7 +26419,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.0543</v>
+        <v>0.04430000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -22899,7 +26449,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.0591</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="6">
@@ -22918,10 +26468,10 @@
         <v>1200</v>
       </c>
       <c r="E6" t="n">
-        <v>1.491319583861974</v>
+        <v>0.4489212217671813</v>
       </c>
       <c r="F6" t="n">
-        <v>1789.583500634369</v>
+        <v>538.7054661206175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -22929,7 +26479,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.0591</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="7">
@@ -22948,10 +26498,10 @@
         <v>500</v>
       </c>
       <c r="E7" t="n">
-        <v>11.02057066247544</v>
+        <v>7.955403539169664</v>
       </c>
       <c r="F7" t="n">
-        <v>5510.285331237721</v>
+        <v>3977.701769584832</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -22959,7 +26509,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.0591</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="8">
@@ -22978,10 +26528,10 @@
         <v>6400</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2195388976847989</v>
+        <v>0.15</v>
       </c>
       <c r="F8" t="n">
-        <v>1405.048945182713</v>
+        <v>960</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -22989,7 +26539,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.1168</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="9">
@@ -23008,10 +26558,10 @@
         <v>960.0000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>8.453072370376614</v>
+        <v>6.193864072554316</v>
       </c>
       <c r="F9" t="n">
-        <v>8114.94947556155</v>
+        <v>5946.109509652144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -23019,7 +26569,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.1168</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="10">
@@ -23049,7 +26599,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.1168</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="11">
@@ -23068,10 +26618,10 @@
         <v>8000</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1509084249290815</v>
+        <v>0.15</v>
       </c>
       <c r="F11" t="n">
-        <v>1207.267399432652</v>
+        <v>1200</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -23079,7 +26629,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.1076</v>
+        <v>0.0926</v>
       </c>
     </row>
     <row r="12">
@@ -23098,10 +26648,10 @@
         <v>1200</v>
       </c>
       <c r="E12" t="n">
-        <v>7.473110149953545</v>
+        <v>5.661287535149168</v>
       </c>
       <c r="F12" t="n">
-        <v>8967.732179944254</v>
+        <v>6793.545042179002</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -23109,7 +26659,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.1076</v>
+        <v>0.0926</v>
       </c>
     </row>
     <row r="13">
@@ -23139,7 +26689,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.1076</v>
+        <v>0.0926</v>
       </c>
     </row>
     <row r="14">
@@ -23158,10 +26708,10 @@
         <v>5600</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3041134101174579</v>
+        <v>0.15</v>
       </c>
       <c r="F14" t="n">
-        <v>1703.035096657764</v>
+        <v>840</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -23169,7 +26719,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.126</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="15">
@@ -23188,10 +26738,10 @@
         <v>840.0000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>9.326737736783304</v>
+        <v>6.7072360785546</v>
       </c>
       <c r="F15" t="n">
-        <v>7834.459698897977</v>
+        <v>5634.078305985865</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -23199,7 +26749,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.126</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="16">
@@ -23229,7 +26779,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.126</v>
+        <v>0.101</v>
       </c>
     </row>
   </sheetData>
@@ -23243,7 +26793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23265,7 +26815,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4436.48015403459</v>
+        <v>4427.670922530242</v>
       </c>
     </row>
     <row r="3">
@@ -23305,7 +26855,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>905.8158993323597</v>
+        <v>902.8129539779802</v>
       </c>
     </row>
     <row r="7">
@@ -23315,7 +26865,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>930.7263431866077</v>
+        <v>856.8377852987155</v>
       </c>
     </row>
     <row r="8">
@@ -23325,7 +26875,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>275.0113515462801</v>
+        <v>242.1092857206584</v>
       </c>
     </row>
     <row r="9">
@@ -23335,7 +26885,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16199.84000777069</v>
+        <v>16088.48463661783</v>
       </c>
     </row>
     <row r="10">
@@ -23345,7 +26895,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.20182780153445</v>
+        <v>50.19079107744346</v>
       </c>
     </row>
     <row r="11">
@@ -23355,7 +26905,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.14713475736083</v>
+        <v>2.910742062080139</v>
       </c>
     </row>
     <row r="12">
@@ -23365,33 +26915,35 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16260.18897032959</v>
+        <v>16141.58616975735</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>drc_nonsec</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>135.6991729661765</v>
+          <t>binding_scenario</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>drc_sec_nonctp</t>
+          <t>drc_nonsec</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>135.6991729661765</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>drc_sec_ctp</t>
+          <t>drc_sec_nonctp</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -23401,47 +26953,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>drc_total</t>
+          <t>drc_sec_ctp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>135.6991729661765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rrao_total</t>
+          <t>drc_total</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80</v>
+        <v>135.6991729661765</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>girr_delta</t>
+          <t>rrao_total</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4436.48015403459</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>girr_vega</t>
+          <t>girr_delta</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4427.670922530242</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>girr_curvature</t>
+          <t>girr_vega</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -23451,27 +27003,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>csr_nonsec_delta</t>
+          <t>girr_curvature</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9712.155222229752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>csr_nonsec_vega</t>
+          <t>csr_nonsec_delta</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>9712.155222229752</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>csr_nonsec_curvature</t>
+          <t>csr_nonsec_vega</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -23481,7 +27033,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>csr_sec_nonctp_delta</t>
+          <t>csr_nonsec_curvature</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -23491,7 +27043,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>csr_sec_nonctp_vega</t>
+          <t>csr_sec_nonctp_delta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -23501,7 +27053,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>csr_sec_nonctp_curvature</t>
+          <t>csr_sec_nonctp_vega</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -23511,7 +27063,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>csr_sec_ctp_delta</t>
+          <t>csr_sec_nonctp_curvature</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -23521,7 +27073,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>csr_sec_ctp_vega</t>
+          <t>csr_sec_ctp_delta</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -23531,7 +27083,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>csr_sec_ctp_curvature</t>
+          <t>csr_sec_ctp_vega</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -23541,57 +27093,57 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>equity_delta</t>
+          <t>csr_sec_ctp_curvature</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>882.3409430639695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equity_vega</t>
+          <t>equity_delta</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.32782151102937</v>
+        <v>882.3409430639695</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>equity_curvature</t>
+          <t>equity_vega</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.14713475736083</v>
+        <v>17.56126885193071</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>commodity_delta</t>
+          <t>equity_curvature</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>930.7263431866077</v>
+        <v>2.910742062080139</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>commodity_vega</t>
+          <t>commodity_delta</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>856.8377852987155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>commodity_curvature</t>
+          <t>commodity_vega</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -23601,30 +27153,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fx_delta</t>
+          <t>commodity_curvature</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>238.137345255775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fx_vega</t>
+          <t>fx_delta</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36.87400629050508</v>
+        <v>209.4797634951456</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>fx_vega</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>32.62952222551276</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>fx_curvature</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B39" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/reports/e2e/E2E_Results.xlsx
+++ b/output/reports/e2e/E2E_Results.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.606</v>
+        <v>0.611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.466</v>
+        <v>0.654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1794,18 +1794,22 @@
         <v>331502.8314298259</v>
       </c>
       <c r="M6" t="n">
-        <v>204466.0667840441</v>
+        <v>206232.795394049</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>16414.44813474237</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.175496781551914</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="R6" t="n">
         <v>48500</v>
       </c>
@@ -1816,7 +1820,7 @@
         <v>7377.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1774376.048315429</v>
+        <v>1776142.776925434</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="b">
@@ -1829,16 +1833,16 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1774376.048315429</v>
+        <v>1776142.776925435</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1172243055227626</v>
+        <v>0.1171077025463321</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1307501869292352</v>
+        <v>0.1306201297632165</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1570267228713577</v>
+        <v>0.1568705284440649</v>
       </c>
       <c r="AD6" t="n">
         <v>3753092.761918609</v>
@@ -1859,7 +1863,7 @@
         <v>0.11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.00722430552276257</v>
+        <v>0.007107702546332056</v>
       </c>
       <c r="AK6" t="n">
         <v>0.03</v>
@@ -2705,18 +2709,22 @@
         <v>331502.8314298259</v>
       </c>
       <c r="M6" t="n">
-        <v>204466.0667840441</v>
+        <v>206232.795394049</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>16414.44813474237</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.175496781551914</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="R6" t="n">
         <v>48500</v>
       </c>
@@ -2727,7 +2735,7 @@
         <v>7377.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1780190.084801815</v>
+        <v>1781956.81341182</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="b">
@@ -2740,16 +2748,16 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1780190.084801815</v>
+        <v>1781956.81341182</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1168414551770499</v>
+        <v>0.1167256122227526</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1303231615436326</v>
+        <v>0.1301939520946086</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1565138792689211</v>
+        <v>0.1563587029221735</v>
       </c>
       <c r="AD6" t="n">
         <v>3753092.761918609</v>
@@ -2770,7 +2778,7 @@
         <v>0.11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.006841455177049913</v>
+        <v>0.006725612222752558</v>
       </c>
       <c r="AK6" t="n">
         <v>0.03</v>
@@ -6673,7 +6681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6996,7 +7004,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7005,13 +7013,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4427.009268437907</v>
+        <v>4427.009268437909</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7020,13 +7028,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9787.49380555365</v>
+        <v>9787.493805553651</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7041,7 +7049,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7056,15 +7064,90 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>237.2787670821237</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GIRR</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4427.009268437907</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CSR_NONSEC</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9787.49380555365</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>902.8587176988991</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1059.807575969784</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C31" t="n">
         <v>237.2787670821237</v>
       </c>
     </row>
@@ -7585,16 +7668,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1774376.048315429</v>
+        <v>1776142.776925434</v>
       </c>
       <c r="G14" t="n">
-        <v>887188.0241577147</v>
+        <v>888071.3884627172</v>
       </c>
       <c r="H14" t="n">
-        <v>1153344.431405029</v>
+        <v>1154492.805001533</v>
       </c>
       <c r="I14" t="n">
-        <v>266156.4072473145</v>
+        <v>266421.4165388153</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -7621,16 +7704,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>1774376.048315429</v>
+        <v>1776142.776925434</v>
       </c>
       <c r="G15" t="n">
-        <v>1064625.628989258</v>
+        <v>1065685.666155261</v>
       </c>
       <c r="H15" t="n">
-        <v>1153344.431405029</v>
+        <v>1154492.805001533</v>
       </c>
       <c r="I15" t="n">
-        <v>88718.80241577154</v>
+        <v>88807.13884627205</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -7657,13 +7740,13 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1774376.048315429</v>
+        <v>1776142.776925434</v>
       </c>
       <c r="G16" t="n">
-        <v>1242063.2338208</v>
+        <v>1243299.943847804</v>
       </c>
       <c r="H16" t="n">
-        <v>1242063.2338208</v>
+        <v>1243299.943847804</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8233,16 +8316,16 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1774376.048315429</v>
+        <v>1776142.776925434</v>
       </c>
       <c r="G32" t="n">
-        <v>887188.0241577147</v>
+        <v>888071.3884627172</v>
       </c>
       <c r="H32" t="n">
-        <v>1286422.635028686</v>
+        <v>1287703.51327094</v>
       </c>
       <c r="I32" t="n">
-        <v>399234.6108709715</v>
+        <v>399632.1248082228</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -8269,16 +8352,16 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>1774376.048315429</v>
+        <v>1776142.776925434</v>
       </c>
       <c r="G33" t="n">
-        <v>1064625.628989258</v>
+        <v>1065685.666155261</v>
       </c>
       <c r="H33" t="n">
-        <v>1286422.635028686</v>
+        <v>1287703.51327094</v>
       </c>
       <c r="I33" t="n">
-        <v>221797.0060394286</v>
+        <v>222017.8471156795</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8305,16 +8388,16 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>1774376.048315429</v>
+        <v>1776142.776925434</v>
       </c>
       <c r="G34" t="n">
-        <v>1242063.2338208</v>
+        <v>1243299.943847804</v>
       </c>
       <c r="H34" t="n">
-        <v>1286422.635028686</v>
+        <v>1287703.51327094</v>
       </c>
       <c r="I34" t="n">
-        <v>44359.40120788569</v>
+        <v>44403.56942313611</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
